--- a/data/raw/irms/roots/EliseLabRootsFINAL2.xlsx
+++ b/data/raw/irms/roots/EliseLabRootsFINAL2.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{C5884EE1-CB2C-4A84-BD17-7646F53765AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56B929CA-3CFC-402D-82FE-9DAC1C2C2243}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="raw" sheetId="1" r:id="rId1"/>
@@ -3397,56 +3397,56 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AZ335"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="6" width="7.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" customWidth="1"/>
-    <col min="11" max="11" width="5.85546875" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" customWidth="1"/>
-    <col min="13" max="14" width="5.5703125" customWidth="1"/>
-    <col min="15" max="15" width="3.5703125" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" customWidth="1"/>
-    <col min="17" max="17" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="21.28515625" customWidth="1"/>
-    <col min="19" max="19" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="30.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.42578125" customWidth="1"/>
-    <col min="24" max="24" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="5" max="6" width="7.7265625" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" customWidth="1"/>
+    <col min="8" max="8" width="9.7265625" customWidth="1"/>
+    <col min="9" max="9" width="10.7265625" customWidth="1"/>
+    <col min="10" max="10" width="5.7265625" customWidth="1"/>
+    <col min="11" max="11" width="5.81640625" customWidth="1"/>
+    <col min="12" max="12" width="5.1796875" customWidth="1"/>
+    <col min="13" max="14" width="5.54296875" customWidth="1"/>
+    <col min="15" max="15" width="3.54296875" customWidth="1"/>
+    <col min="16" max="16" width="4.81640625" customWidth="1"/>
+    <col min="17" max="17" width="19.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.26953125" customWidth="1"/>
+    <col min="19" max="19" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="30.54296875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.453125" customWidth="1"/>
+    <col min="24" max="24" width="22.7265625" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="23" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" customWidth="1"/>
-    <col min="33" max="33" width="11.28515625" customWidth="1"/>
+    <col min="26" max="26" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7265625" customWidth="1"/>
+    <col min="33" max="33" width="11.26953125" customWidth="1"/>
     <col min="34" max="34" width="13" customWidth="1"/>
-    <col min="35" max="35" width="12.140625" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" customWidth="1"/>
-    <col min="37" max="37" width="12.140625" customWidth="1"/>
-    <col min="38" max="38" width="13.7109375" customWidth="1"/>
-    <col min="39" max="39" width="22.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="43" max="44" width="36.140625" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="24.5703125" bestFit="1" customWidth="1"/>
-    <col min="50" max="52" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.1796875" customWidth="1"/>
+    <col min="36" max="36" width="12.26953125" customWidth="1"/>
+    <col min="37" max="37" width="12.1796875" customWidth="1"/>
+    <col min="38" max="38" width="13.7265625" customWidth="1"/>
+    <col min="39" max="39" width="22.7265625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="27.54296875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="18.81640625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="35.81640625" bestFit="1" customWidth="1"/>
+    <col min="43" max="44" width="36.1796875" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="40.26953125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="25.7265625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="23.7265625" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="24.54296875" bestFit="1" customWidth="1"/>
+    <col min="50" max="52" width="26.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:52" ht="31" x14ac:dyDescent="0.35">
       <c r="A1" s="10" t="s">
         <v>21</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="2" spans="1:52" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:52" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A2" s="10"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -3672,7 +3672,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="3" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>-5.3244169427735253</v>
       </c>
     </row>
-    <row r="4" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -3980,7 +3980,7 @@
         <v>7.4762608501921513</v>
       </c>
     </row>
-    <row r="5" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -4134,7 +4134,7 @@
         <v>6.9952936876060967</v>
       </c>
     </row>
-    <row r="6" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>1</v>
       </c>
@@ -4288,7 +4288,7 @@
         <v>9.4967314350991057</v>
       </c>
     </row>
-    <row r="7" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>1</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>15.365658453763142</v>
       </c>
     </row>
-    <row r="8" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>1</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>16.230545780042682</v>
       </c>
     </row>
-    <row r="9" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>1</v>
       </c>
@@ -4753,7 +4753,7 @@
         <v>-1.2030850909905413</v>
       </c>
     </row>
-    <row r="10" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>1</v>
       </c>
@@ -4908,7 +4908,7 @@
         <v>22.336451425768455</v>
       </c>
     </row>
-    <row r="11" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>1</v>
       </c>
@@ -5063,7 +5063,7 @@
         <v>6.5994037387739901</v>
       </c>
     </row>
-    <row r="12" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>1</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>18.547934826012025</v>
       </c>
     </row>
-    <row r="13" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>1</v>
       </c>
@@ -5373,7 +5373,7 @@
         <v>7.3310352709321505</v>
       </c>
     </row>
-    <row r="14" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>1</v>
       </c>
@@ -5528,7 +5528,7 @@
         <v>22.275702691121335</v>
       </c>
     </row>
-    <row r="15" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I15" s="25" t="s">
         <v>469</v>
       </c>
@@ -5662,7 +5662,7 @@
         <v>28.132506819327215</v>
       </c>
     </row>
-    <row r="16" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>1</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>5.0692805042840128</v>
       </c>
     </row>
-    <row r="17" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>1</v>
       </c>
@@ -5972,7 +5972,7 @@
         <v>36.230825698042594</v>
       </c>
     </row>
-    <row r="18" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>1</v>
       </c>
@@ -6127,7 +6127,7 @@
         <v>13.879778274190624</v>
       </c>
     </row>
-    <row r="19" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>1</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>19.651766145958316</v>
       </c>
     </row>
-    <row r="20" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>1</v>
       </c>
@@ -6437,7 +6437,7 @@
         <v>14.842984840877095</v>
       </c>
     </row>
-    <row r="21" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>1</v>
       </c>
@@ -6592,7 +6592,7 @@
         <v>19.551475240464633</v>
       </c>
     </row>
-    <row r="22" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>1</v>
       </c>
@@ -6747,7 +6747,7 @@
         <v>1.5444138152065356</v>
       </c>
     </row>
-    <row r="23" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>1</v>
       </c>
@@ -6902,7 +6902,7 @@
         <v>29.462021533541719</v>
       </c>
     </row>
-    <row r="24" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>1</v>
       </c>
@@ -7057,7 +7057,7 @@
         <v>14.527844129006429</v>
       </c>
     </row>
-    <row r="25" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>1</v>
       </c>
@@ -7212,7 +7212,7 @@
         <v>15.883215135659157</v>
       </c>
     </row>
-    <row r="26" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>1</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>1.4497178838301927</v>
       </c>
     </row>
-    <row r="27" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>1</v>
       </c>
@@ -7522,7 +7522,7 @@
         <v>21.384487617990278</v>
       </c>
     </row>
-    <row r="28" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I28" s="25" t="s">
         <v>469</v>
       </c>
@@ -7656,7 +7656,7 @@
         <v>26.753141026636396</v>
       </c>
     </row>
-    <row r="29" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I29" s="25" t="s">
         <v>469</v>
       </c>
@@ -7790,7 +7790,7 @@
         <v>34.769657483357804</v>
       </c>
     </row>
-    <row r="30" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>1</v>
       </c>
@@ -7945,7 +7945,7 @@
         <v>-15.507829776952864</v>
       </c>
     </row>
-    <row r="31" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>1</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>-21.909277947707029</v>
       </c>
     </row>
-    <row r="32" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>1</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>-6.6431796576416069</v>
       </c>
     </row>
-    <row r="33" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>1</v>
       </c>
@@ -8410,7 +8410,7 @@
         <v>-0.14932473304973826</v>
       </c>
     </row>
-    <row r="34" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>1</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>-5.8125990255741833</v>
       </c>
     </row>
-    <row r="35" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>1</v>
       </c>
@@ -8720,7 +8720,7 @@
         <v>19.886492701135516</v>
       </c>
     </row>
-    <row r="36" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>1</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>-10.135072198684814</v>
       </c>
     </row>
-    <row r="37" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>1</v>
       </c>
@@ -9030,7 +9030,7 @@
         <v>-13.063865793820906</v>
       </c>
     </row>
-    <row r="38" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>1</v>
       </c>
@@ -9185,7 +9185,7 @@
         <v>-5.6721436809437087</v>
       </c>
     </row>
-    <row r="39" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>1</v>
       </c>
@@ -9340,7 +9340,7 @@
         <v>-8.6584204462503145</v>
       </c>
     </row>
-    <row r="40" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>1</v>
       </c>
@@ -9495,7 +9495,7 @@
         <v>-3.2969350751255178</v>
       </c>
     </row>
-    <row r="41" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>1</v>
       </c>
@@ -9650,7 +9650,7 @@
         <v>15.540748943556613</v>
       </c>
     </row>
-    <row r="42" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I42" s="25" t="s">
         <v>469</v>
       </c>
@@ -9784,7 +9784,7 @@
         <v>25.491911714283777</v>
       </c>
     </row>
-    <row r="43" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>1</v>
       </c>
@@ -9939,7 +9939,7 @@
         <v>-23.759226673198963</v>
       </c>
     </row>
-    <row r="44" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>1</v>
       </c>
@@ -10094,7 +10094,7 @@
         <v>-24.007322018404498</v>
       </c>
     </row>
-    <row r="45" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>1</v>
       </c>
@@ -10249,7 +10249,7 @@
         <v>-12.927403420490702</v>
       </c>
     </row>
-    <row r="46" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>1</v>
       </c>
@@ -10404,7 +10404,7 @@
         <v>-19.636068357560266</v>
       </c>
     </row>
-    <row r="47" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>1</v>
       </c>
@@ -10559,7 +10559,7 @@
         <v>-12.072878974422885</v>
       </c>
     </row>
-    <row r="48" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A48" s="13">
         <v>1</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>-20.648989283758024</v>
       </c>
     </row>
-    <row r="49" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>1</v>
       </c>
@@ -10869,7 +10869,7 @@
         <v>-18.418059953790866</v>
       </c>
     </row>
-    <row r="50" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>1</v>
       </c>
@@ -11024,7 +11024,7 @@
         <v>-11.061590105845287</v>
       </c>
     </row>
-    <row r="51" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>1</v>
       </c>
@@ -11179,7 +11179,7 @@
         <v>2.346828293546821</v>
       </c>
     </row>
-    <row r="52" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>1</v>
       </c>
@@ -11334,7 +11334,7 @@
         <v>-3.5499515637527068</v>
       </c>
     </row>
-    <row r="53" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A53">
         <v>1</v>
       </c>
@@ -11489,7 +11489,7 @@
         <v>15.734577584693987</v>
       </c>
     </row>
-    <row r="54" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A54" s="13">
         <v>2</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>16.665139265799045</v>
       </c>
     </row>
-    <row r="55" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I55" s="25" t="s">
         <v>469</v>
       </c>
@@ -11778,7 +11778,7 @@
         <v>26.148622239365871</v>
       </c>
     </row>
-    <row r="56" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A56">
         <v>2</v>
       </c>
@@ -11933,7 +11933,7 @@
         <v>17.784775262652541</v>
       </c>
     </row>
-    <row r="57" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A57">
         <v>2</v>
       </c>
@@ -12088,7 +12088,7 @@
         <v>15.219048009809111</v>
       </c>
     </row>
-    <row r="58" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A58">
         <v>2</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>13.204014021752641</v>
       </c>
     </row>
-    <row r="59" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A59">
         <v>2</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>31.787552054489687</v>
       </c>
     </row>
-    <row r="60" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A60">
         <v>2</v>
       </c>
@@ -12553,7 +12553,7 @@
         <v>35.689587892746566</v>
       </c>
     </row>
-    <row r="61" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A61">
         <v>2</v>
       </c>
@@ -12708,7 +12708,7 @@
         <v>2.6404056540685339</v>
       </c>
     </row>
-    <row r="62" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A62">
         <v>2</v>
       </c>
@@ -12863,7 +12863,7 @@
         <v>28.571759230215932</v>
       </c>
     </row>
-    <row r="63" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A63">
         <v>2</v>
       </c>
@@ -13018,7 +13018,7 @@
         <v>7.9959658469408446</v>
       </c>
     </row>
-    <row r="64" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A64">
         <v>2</v>
       </c>
@@ -13173,7 +13173,7 @@
         <v>15.791264292464025</v>
       </c>
     </row>
-    <row r="65" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A65">
         <v>2</v>
       </c>
@@ -13328,7 +13328,7 @@
         <v>10.691756753840043</v>
       </c>
     </row>
-    <row r="66" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A66">
         <v>2</v>
       </c>
@@ -13483,7 +13483,7 @@
         <v>38.795023880133776</v>
       </c>
     </row>
-    <row r="67" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A67">
         <v>2</v>
       </c>
@@ -13641,7 +13641,7 @@
         <v>56.515869319642142</v>
       </c>
     </row>
-    <row r="68" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I68" s="25" t="s">
         <v>469</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>25.819098391024475</v>
       </c>
     </row>
-    <row r="69" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A69">
         <v>2</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>60.351715928450567</v>
       </c>
     </row>
-    <row r="70" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A70">
         <v>2</v>
       </c>
@@ -14091,7 +14091,7 @@
         <v>3.9733385842177782</v>
       </c>
     </row>
-    <row r="71" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A71">
         <v>2</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>15.078548008766735</v>
       </c>
     </row>
-    <row r="72" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A72">
         <v>2</v>
       </c>
@@ -14401,7 +14401,7 @@
         <v>17.384242332534328</v>
       </c>
     </row>
-    <row r="73" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A73">
         <v>2</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>26.346655837266031</v>
       </c>
     </row>
-    <row r="74" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A74">
         <v>2</v>
       </c>
@@ -14711,7 +14711,7 @@
         <v>37.853197091921587</v>
       </c>
     </row>
-    <row r="75" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A75">
         <v>2</v>
       </c>
@@ -14866,7 +14866,7 @@
         <v>25.766690211803667</v>
       </c>
     </row>
-    <row r="76" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A76">
         <v>2</v>
       </c>
@@ -15021,7 +15021,7 @@
         <v>11.96095688313692</v>
       </c>
     </row>
-    <row r="77" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A77">
         <v>2</v>
       </c>
@@ -15176,7 +15176,7 @@
         <v>12.65975719979995</v>
       </c>
     </row>
-    <row r="78" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A78">
         <v>2</v>
       </c>
@@ -15331,7 +15331,7 @@
         <v>25.831534669980005</v>
       </c>
     </row>
-    <row r="79" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A79">
         <v>2</v>
       </c>
@@ -15486,7 +15486,7 @@
         <v>9.1466401525552854</v>
       </c>
     </row>
-    <row r="80" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A80">
         <v>2</v>
       </c>
@@ -15641,7 +15641,7 @@
         <v>16.068377852402893</v>
       </c>
     </row>
-    <row r="81" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I81" s="25" t="s">
         <v>469</v>
       </c>
@@ -15775,7 +15775,7 @@
         <v>27.100531742443312</v>
       </c>
     </row>
-    <row r="82" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A82">
         <v>2</v>
       </c>
@@ -15930,7 +15930,7 @@
         <v>25.961303582526796</v>
       </c>
     </row>
-    <row r="83" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A83">
         <v>2</v>
       </c>
@@ -16085,7 +16085,7 @@
         <v>7.194066647853159</v>
       </c>
     </row>
-    <row r="84" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A84">
         <v>2</v>
       </c>
@@ -16240,7 +16240,7 @@
         <v>18.491210485580556</v>
       </c>
     </row>
-    <row r="85" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A85">
         <v>2</v>
       </c>
@@ -16395,7 +16395,7 @@
         <v>10.847211045783567</v>
       </c>
     </row>
-    <row r="86" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A86">
         <v>2</v>
       </c>
@@ -16550,7 +16550,7 @@
         <v>-8.078925738081999</v>
       </c>
     </row>
-    <row r="87" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A87">
         <v>2</v>
       </c>
@@ -16705,7 +16705,7 @@
         <v>62.004772727035636</v>
       </c>
     </row>
-    <row r="88" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A88">
         <v>2</v>
       </c>
@@ -16860,7 +16860,7 @@
         <v>42.820314867457739</v>
       </c>
     </row>
-    <row r="89" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A89">
         <v>2</v>
       </c>
@@ -17015,7 +17015,7 @@
         <v>16.259930706703507</v>
       </c>
     </row>
-    <row r="90" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A90">
         <v>2</v>
       </c>
@@ -17170,7 +17170,7 @@
         <v>23.376634584646446</v>
       </c>
     </row>
-    <row r="91" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A91">
         <v>2</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>13.905410430545828</v>
       </c>
     </row>
-    <row r="92" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A92">
         <v>2</v>
       </c>
@@ -17480,7 +17480,7 @@
         <v>19.102495323024549</v>
       </c>
     </row>
-    <row r="93" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A93">
         <v>2</v>
       </c>
@@ -17635,7 +17635,7 @@
         <v>22.98579685527713</v>
       </c>
     </row>
-    <row r="94" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I94" s="25" t="s">
         <v>469</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>24.843083571290947</v>
       </c>
     </row>
-    <row r="95" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A95">
         <v>2</v>
       </c>
@@ -17924,7 +17924,7 @@
         <v>25.295615915854608</v>
       </c>
     </row>
-    <row r="96" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A96">
         <v>2</v>
       </c>
@@ -18079,7 +18079,7 @@
         <v>-4.0183883665156905</v>
       </c>
     </row>
-    <row r="97" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A97">
         <v>2</v>
       </c>
@@ -18234,7 +18234,7 @@
         <v>13.620583672548925</v>
       </c>
     </row>
-    <row r="98" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A98">
         <v>2</v>
       </c>
@@ -18389,7 +18389,7 @@
         <v>40.800081165197625</v>
       </c>
     </row>
-    <row r="99" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A99">
         <v>2</v>
       </c>
@@ -18544,7 +18544,7 @@
         <v>29.972927722388132</v>
       </c>
     </row>
-    <row r="100" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A100">
         <v>2</v>
       </c>
@@ -18699,7 +18699,7 @@
         <v>7.9488463025767508</v>
       </c>
     </row>
-    <row r="101" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A101">
         <v>2</v>
       </c>
@@ -18854,7 +18854,7 @@
         <v>3.7869454832883953</v>
       </c>
     </row>
-    <row r="102" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A102">
         <v>2</v>
       </c>
@@ -19009,7 +19009,7 @@
         <v>7.4003659563848245</v>
       </c>
     </row>
-    <row r="103" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A103">
         <v>2</v>
       </c>
@@ -19164,7 +19164,7 @@
         <v>14.696366506086189</v>
       </c>
     </row>
-    <row r="104" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A104">
         <v>3</v>
       </c>
@@ -19319,7 +19319,7 @@
         <v>62.48543473915236</v>
       </c>
     </row>
-    <row r="105" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A105">
         <v>3</v>
       </c>
@@ -19474,7 +19474,7 @@
         <v>37.516290895776017</v>
       </c>
     </row>
-    <row r="106" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A106">
         <v>3</v>
       </c>
@@ -19629,7 +19629,7 @@
         <v>7.593533834717725</v>
       </c>
     </row>
-    <row r="107" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I107" s="25" t="s">
         <v>469</v>
       </c>
@@ -19763,7 +19763,7 @@
         <v>24.672609080109709</v>
       </c>
     </row>
-    <row r="108" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A108">
         <v>3</v>
       </c>
@@ -19918,7 +19918,7 @@
         <v>15.461977886515042</v>
       </c>
     </row>
-    <row r="109" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A109">
         <v>3</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>7.284794607489431</v>
       </c>
     </row>
-    <row r="110" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A110">
         <v>3</v>
       </c>
@@ -20228,7 +20228,7 @@
         <v>11.580366855012958</v>
       </c>
     </row>
-    <row r="111" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A111">
         <v>3</v>
       </c>
@@ -20383,7 +20383,7 @@
         <v>95.367712532918873</v>
       </c>
     </row>
-    <row r="112" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A112">
         <v>3</v>
       </c>
@@ -20538,7 +20538,7 @@
         <v>66.692618718555693</v>
       </c>
     </row>
-    <row r="113" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A113">
         <v>3</v>
       </c>
@@ -20693,7 +20693,7 @@
         <v>55.754802496730264</v>
       </c>
     </row>
-    <row r="114" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A114">
         <v>3</v>
       </c>
@@ -20848,7 +20848,7 @@
         <v>29.131015973142826</v>
       </c>
     </row>
-    <row r="115" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A115">
         <v>3</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>4.9783064151820442</v>
       </c>
     </row>
-    <row r="116" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A116">
         <v>3</v>
       </c>
@@ -21158,7 +21158,7 @@
         <v>17.947699343838774</v>
       </c>
     </row>
-    <row r="117" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A117">
         <v>3</v>
       </c>
@@ -21313,7 +21313,7 @@
         <v>92.55704934699294</v>
       </c>
     </row>
-    <row r="118" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A118">
         <v>3</v>
       </c>
@@ -21468,7 +21468,7 @@
         <v>55.065776228873098</v>
       </c>
     </row>
-    <row r="119" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A119">
         <v>3</v>
       </c>
@@ -21623,7 +21623,7 @@
         <v>19.417202740654727</v>
       </c>
     </row>
-    <row r="120" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I120" s="25" t="s">
         <v>469</v>
       </c>
@@ -21757,7 +21757,7 @@
         <v>28.033006413941131</v>
       </c>
     </row>
-    <row r="121" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A121">
         <v>3</v>
       </c>
@@ -21912,7 +21912,7 @@
         <v>20.758755722840583</v>
       </c>
     </row>
-    <row r="122" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A122">
         <v>3</v>
       </c>
@@ -22067,7 +22067,7 @@
         <v>13.351083420030108</v>
       </c>
     </row>
-    <row r="123" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A123">
         <v>3</v>
       </c>
@@ -22222,7 +22222,7 @@
         <v>21.001449417599183</v>
       </c>
     </row>
-    <row r="124" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A124">
         <v>3</v>
       </c>
@@ -22377,7 +22377,7 @@
         <v>13.702955888494905</v>
       </c>
     </row>
-    <row r="125" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A125">
         <v>3</v>
       </c>
@@ -22532,7 +22532,7 @@
         <v>3.548073118524453</v>
       </c>
     </row>
-    <row r="126" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A126">
         <v>3</v>
       </c>
@@ -22687,7 +22687,7 @@
         <v>31.301592136399048</v>
       </c>
     </row>
-    <row r="127" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A127">
         <v>3</v>
       </c>
@@ -22842,7 +22842,7 @@
         <v>27.89330917031041</v>
       </c>
     </row>
-    <row r="128" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A128">
         <v>3</v>
       </c>
@@ -22997,7 +22997,7 @@
         <v>12.606275150597313</v>
       </c>
     </row>
-    <row r="129" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A129">
         <v>3</v>
       </c>
@@ -23152,7 +23152,7 @@
         <v>27.020042077479101</v>
       </c>
     </row>
-    <row r="130" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A130">
         <v>3</v>
       </c>
@@ -23307,7 +23307,7 @@
         <v>14.906319833334347</v>
       </c>
     </row>
-    <row r="131" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A131">
         <v>3</v>
       </c>
@@ -23462,7 +23462,7 @@
         <v>8.4947505373578203</v>
       </c>
     </row>
-    <row r="132" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A132">
         <v>3</v>
       </c>
@@ -23617,7 +23617,7 @@
         <v>64.219490858574702</v>
       </c>
     </row>
-    <row r="133" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I133" s="25" t="s">
         <v>469</v>
       </c>
@@ -23751,7 +23751,7 @@
         <v>35.952643870333922</v>
       </c>
     </row>
-    <row r="134" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A134">
         <v>3</v>
       </c>
@@ -23906,7 +23906,7 @@
         <v>34.74466443351254</v>
       </c>
     </row>
-    <row r="135" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A135">
         <v>3</v>
       </c>
@@ -24061,7 +24061,7 @@
         <v>1.8530535675331805</v>
       </c>
     </row>
-    <row r="136" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A136">
         <v>3</v>
       </c>
@@ -24216,7 +24216,7 @@
         <v>31.109090383014681</v>
       </c>
     </row>
-    <row r="137" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A137">
         <v>3</v>
       </c>
@@ -24371,7 +24371,7 @@
         <v>29.958957031468444</v>
       </c>
     </row>
-    <row r="138" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A138">
         <v>3</v>
       </c>
@@ -24529,7 +24529,7 @@
         <v>-1.6848069852248848</v>
       </c>
     </row>
-    <row r="139" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A139">
         <v>3</v>
       </c>
@@ -24684,7 +24684,7 @@
         <v>53.919571607328187</v>
       </c>
     </row>
-    <row r="140" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A140">
         <v>3</v>
       </c>
@@ -24839,7 +24839,7 @@
         <v>42.76664463077617</v>
       </c>
     </row>
-    <row r="141" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A141">
         <v>3</v>
       </c>
@@ -24994,7 +24994,7 @@
         <v>15.59378725067395</v>
       </c>
     </row>
-    <row r="142" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A142">
         <v>3</v>
       </c>
@@ -25149,7 +25149,7 @@
         <v>30.533660363714077</v>
       </c>
     </row>
-    <row r="143" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A143">
         <v>3</v>
       </c>
@@ -25304,7 +25304,7 @@
         <v>62.281562868100607</v>
       </c>
     </row>
-    <row r="144" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A144">
         <v>3</v>
       </c>
@@ -25459,7 +25459,7 @@
         <v>22.778575429192038</v>
       </c>
     </row>
-    <row r="145" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A145">
         <v>3</v>
       </c>
@@ -25614,7 +25614,7 @@
         <v>79.094266030972364</v>
       </c>
     </row>
-    <row r="146" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I146" s="25" t="s">
         <v>469</v>
       </c>
@@ -25748,7 +25748,7 @@
         <v>33.906575862074902</v>
       </c>
     </row>
-    <row r="147" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A147">
         <v>3</v>
       </c>
@@ -25903,7 +25903,7 @@
         <v>36.208827759443011</v>
       </c>
     </row>
-    <row r="148" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A148">
         <v>3</v>
       </c>
@@ -26061,7 +26061,7 @@
         <v>29.869769544870195</v>
       </c>
     </row>
-    <row r="149" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A149">
         <v>3</v>
       </c>
@@ -26219,7 +26219,7 @@
         <v>21.930998657144762</v>
       </c>
     </row>
-    <row r="150" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A150">
         <v>3</v>
       </c>
@@ -26374,7 +26374,7 @@
         <v>52.12235231520701</v>
       </c>
     </row>
-    <row r="151" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A151">
         <v>3</v>
       </c>
@@ -26529,7 +26529,7 @@
         <v>26.265788860289074</v>
       </c>
     </row>
-    <row r="152" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A152">
         <v>3</v>
       </c>
@@ -26684,7 +26684,7 @@
         <v>5.8240903822071033</v>
       </c>
     </row>
-    <row r="153" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A153">
         <v>3</v>
       </c>
@@ -26839,7 +26839,7 @@
         <v>26.619707997799221</v>
       </c>
     </row>
-    <row r="154" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A154">
         <v>3</v>
       </c>
@@ -26997,7 +26997,7 @@
         <v>-9.6967820917170933</v>
       </c>
     </row>
-    <row r="155" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A155">
         <v>3</v>
       </c>
@@ -27152,7 +27152,7 @@
         <v>24.669646815347335</v>
       </c>
     </row>
-    <row r="156" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A156">
         <v>4</v>
       </c>
@@ -27307,7 +27307,7 @@
         <v>26.674970205766702</v>
       </c>
     </row>
-    <row r="157" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A157">
         <v>4</v>
       </c>
@@ -27462,7 +27462,7 @@
         <v>32.287692062091807</v>
       </c>
     </row>
-    <row r="158" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A158">
         <v>4</v>
       </c>
@@ -27617,7 +27617,7 @@
         <v>50.619765852664145</v>
       </c>
     </row>
-    <row r="159" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I159" s="25" t="s">
         <v>469</v>
       </c>
@@ -27751,7 +27751,7 @@
         <v>24.143278885555564</v>
       </c>
     </row>
-    <row r="160" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A160">
         <v>4</v>
       </c>
@@ -27906,7 +27906,7 @@
         <v>20.878184364225838</v>
       </c>
     </row>
-    <row r="161" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A161">
         <v>4</v>
       </c>
@@ -28061,7 +28061,7 @@
         <v>10.026673133636255</v>
       </c>
     </row>
-    <row r="162" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A162">
         <v>4</v>
       </c>
@@ -28216,7 +28216,7 @@
         <v>12.623962319338045</v>
       </c>
     </row>
-    <row r="163" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A163">
         <v>4</v>
       </c>
@@ -28371,7 +28371,7 @@
         <v>35.762960912166797</v>
       </c>
     </row>
-    <row r="164" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A164">
         <v>4</v>
       </c>
@@ -28526,7 +28526,7 @@
         <v>54.571596856574089</v>
       </c>
     </row>
-    <row r="165" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A165">
         <v>4</v>
       </c>
@@ -28681,7 +28681,7 @@
         <v>16.777771244318451</v>
       </c>
     </row>
-    <row r="166" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A166">
         <v>4</v>
       </c>
@@ -28836,7 +28836,7 @@
         <v>21.510498700969549</v>
       </c>
     </row>
-    <row r="167" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A167">
         <v>4</v>
       </c>
@@ -28991,7 +28991,7 @@
         <v>4.1038166686657718</v>
       </c>
     </row>
-    <row r="168" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A168">
         <v>4</v>
       </c>
@@ -29146,7 +29146,7 @@
         <v>16.153326373478105</v>
       </c>
     </row>
-    <row r="169" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A169">
         <v>4</v>
       </c>
@@ -29301,7 +29301,7 @@
         <v>47.96002314238379</v>
       </c>
     </row>
-    <row r="170" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A170">
         <v>4</v>
       </c>
@@ -29456,7 +29456,7 @@
         <v>54.15353403719125</v>
       </c>
     </row>
-    <row r="171" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A171">
         <v>4</v>
       </c>
@@ -29611,7 +29611,7 @@
         <v>30.806284326871939</v>
       </c>
     </row>
-    <row r="172" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A172">
         <v>4</v>
       </c>
@@ -29774,7 +29774,7 @@
         <v>118.75181611487263</v>
       </c>
     </row>
-    <row r="173" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A173">
         <v>4</v>
       </c>
@@ -29937,7 +29937,7 @@
         <v>15.018254519700847</v>
       </c>
     </row>
-    <row r="174" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A174">
         <v>4</v>
       </c>
@@ -30100,7 +30100,7 @@
         <v>23.737368401932635</v>
       </c>
     </row>
-    <row r="175" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A175">
         <v>4</v>
       </c>
@@ -30263,7 +30263,7 @@
         <v>4.030757731496859</v>
       </c>
     </row>
-    <row r="176" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A176">
         <v>4</v>
       </c>
@@ -30426,7 +30426,7 @@
         <v>30.182071919533371</v>
       </c>
     </row>
-    <row r="177" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A177">
         <v>4</v>
       </c>
@@ -30589,7 +30589,7 @@
         <v>27.804072438022409</v>
       </c>
     </row>
-    <row r="178" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A178">
         <v>4</v>
       </c>
@@ -30752,7 +30752,7 @@
         <v>69.012767176126474</v>
       </c>
     </row>
-    <row r="179" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A179">
         <v>4</v>
       </c>
@@ -30915,7 +30915,7 @@
         <v>24.131627899157682</v>
       </c>
     </row>
-    <row r="180" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A180">
         <v>4</v>
       </c>
@@ -31078,7 +31078,7 @@
         <v>21.874011479980915</v>
       </c>
     </row>
-    <row r="181" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A181">
         <v>4</v>
       </c>
@@ -31233,7 +31233,7 @@
         <v>-0.24809088830402004</v>
       </c>
     </row>
-    <row r="182" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A182">
         <v>4</v>
       </c>
@@ -31388,7 +31388,7 @@
         <v>0.67617777434136883</v>
       </c>
     </row>
-    <row r="183" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A183">
         <v>4</v>
       </c>
@@ -31543,7 +31543,7 @@
         <v>47.515364120089828</v>
       </c>
     </row>
-    <row r="184" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A184">
         <v>4</v>
       </c>
@@ -31698,7 +31698,7 @@
         <v>58.912795542325199</v>
       </c>
     </row>
-    <row r="185" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A185">
         <v>4</v>
       </c>
@@ -31853,7 +31853,7 @@
         <v>1.3923112348113165</v>
       </c>
     </row>
-    <row r="186" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A186">
         <v>4</v>
       </c>
@@ -32008,7 +32008,7 @@
         <v>16.694710423090786</v>
       </c>
     </row>
-    <row r="187" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A187">
         <v>4</v>
       </c>
@@ -32163,7 +32163,7 @@
         <v>24.078051020677282</v>
       </c>
     </row>
-    <row r="188" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A188">
         <v>4</v>
       </c>
@@ -32318,7 +32318,7 @@
         <v>0.40395757047839709</v>
       </c>
     </row>
-    <row r="189" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A189">
         <v>4</v>
       </c>
@@ -32473,7 +32473,7 @@
         <v>92.329184705310922</v>
       </c>
     </row>
-    <row r="190" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A190">
         <v>4</v>
       </c>
@@ -32628,7 +32628,7 @@
         <v>48.6049270531419</v>
       </c>
     </row>
-    <row r="191" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A191">
         <v>4</v>
       </c>
@@ -32783,7 +32783,7 @@
         <v>27.430565183215183</v>
       </c>
     </row>
-    <row r="192" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A192">
         <v>4</v>
       </c>
@@ -32938,7 +32938,7 @@
         <v>29.263379919854952</v>
       </c>
     </row>
-    <row r="193" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A193">
         <v>4</v>
       </c>
@@ -33093,7 +33093,7 @@
         <v>46.25733072637361</v>
       </c>
     </row>
-    <row r="194" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A194">
         <v>4</v>
       </c>
@@ -33248,7 +33248,7 @@
         <v>29.047199241718502</v>
       </c>
     </row>
-    <row r="195" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A195">
         <v>4</v>
       </c>
@@ -33403,7 +33403,7 @@
         <v>34.313415944129403</v>
       </c>
     </row>
-    <row r="196" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A196">
         <v>4</v>
       </c>
@@ -33558,7 +33558,7 @@
         <v>22.489827848743982</v>
       </c>
     </row>
-    <row r="197" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A197">
         <v>4</v>
       </c>
@@ -33713,7 +33713,7 @@
         <v>5.4339440184603136</v>
       </c>
     </row>
-    <row r="198" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A198">
         <v>4</v>
       </c>
@@ -33868,7 +33868,7 @@
         <v>14.238793509131487</v>
       </c>
     </row>
-    <row r="199" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A199">
         <v>4</v>
       </c>
@@ -34023,7 +34023,7 @@
         <v>56.457663653641802</v>
       </c>
     </row>
-    <row r="200" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A200">
         <v>4</v>
       </c>
@@ -34178,7 +34178,7 @@
         <v>3.4408337352331841</v>
       </c>
     </row>
-    <row r="201" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A201">
         <v>4</v>
       </c>
@@ -34333,7 +34333,7 @@
         <v>38.363478358238723</v>
       </c>
     </row>
-    <row r="202" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A202">
         <v>4</v>
       </c>
@@ -34488,7 +34488,7 @@
         <v>20.927006780027124</v>
       </c>
     </row>
-    <row r="203" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A203">
         <v>4</v>
       </c>
@@ -34643,7 +34643,7 @@
         <v>14.675003840356471</v>
       </c>
     </row>
-    <row r="204" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A204">
         <v>4</v>
       </c>
@@ -34798,7 +34798,7 @@
         <v>28.207043493018169</v>
       </c>
     </row>
-    <row r="205" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A205">
         <v>5</v>
       </c>
@@ -34953,7 +34953,7 @@
         <v>2.2178689712948341</v>
       </c>
     </row>
-    <row r="206" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A206">
         <v>5</v>
       </c>
@@ -35108,7 +35108,7 @@
         <v>-29.067191257081681</v>
       </c>
     </row>
-    <row r="207" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A207">
         <v>5</v>
       </c>
@@ -35263,7 +35263,7 @@
         <v>-7.0850815603695771</v>
       </c>
     </row>
-    <row r="208" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I208" s="25" t="s">
         <v>469</v>
       </c>
@@ -35397,7 +35397,7 @@
         <v>15.226058928929922</v>
       </c>
     </row>
-    <row r="209" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I209" s="25" t="s">
         <v>469</v>
       </c>
@@ -35531,7 +35531,7 @@
         <v>20.848897176604098</v>
       </c>
     </row>
-    <row r="210" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A210">
         <v>5</v>
       </c>
@@ -35689,7 +35689,7 @@
         <v>4.0862288299692295</v>
       </c>
     </row>
-    <row r="211" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A211">
         <v>5</v>
       </c>
@@ -35844,7 +35844,7 @@
         <v>12.583570342679096</v>
       </c>
     </row>
-    <row r="212" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A212">
         <v>5</v>
       </c>
@@ -35999,7 +35999,7 @@
         <v>15.631225582812824</v>
       </c>
     </row>
-    <row r="213" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A213">
         <v>5</v>
       </c>
@@ -36154,7 +36154,7 @@
         <v>11.076435865631229</v>
       </c>
     </row>
-    <row r="214" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A214">
         <v>5</v>
       </c>
@@ -36309,7 +36309,7 @@
         <v>11.840581801909611</v>
       </c>
     </row>
-    <row r="215" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A215">
         <v>5</v>
       </c>
@@ -36464,7 +36464,7 @@
         <v>15.895099035101445</v>
       </c>
     </row>
-    <row r="216" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A216">
         <v>5</v>
       </c>
@@ -36619,7 +36619,7 @@
         <v>42.676780867776372</v>
       </c>
     </row>
-    <row r="217" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A217">
         <v>5</v>
       </c>
@@ -36774,7 +36774,7 @@
         <v>244.02071483255574</v>
       </c>
     </row>
-    <row r="218" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A218">
         <v>5</v>
       </c>
@@ -36929,7 +36929,7 @@
         <v>101.80842893481979</v>
       </c>
     </row>
-    <row r="219" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A219">
         <v>5</v>
       </c>
@@ -37084,7 +37084,7 @@
         <v>62.749917582221038</v>
       </c>
     </row>
-    <row r="220" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A220">
         <v>5</v>
       </c>
@@ -37239,7 +37239,7 @@
         <v>7.1292626649710478</v>
       </c>
     </row>
-    <row r="221" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A221">
         <v>5</v>
       </c>
@@ -37394,7 +37394,7 @@
         <v>72.068670081975043</v>
       </c>
     </row>
-    <row r="222" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I222" s="25" t="s">
         <v>469</v>
       </c>
@@ -37528,7 +37528,7 @@
         <v>28.856639794785362</v>
       </c>
     </row>
-    <row r="223" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A223">
         <v>5</v>
       </c>
@@ -37683,7 +37683,7 @@
         <v>103.11642156628275</v>
       </c>
     </row>
-    <row r="224" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A224">
         <v>5</v>
       </c>
@@ -37838,7 +37838,7 @@
         <v>91.941435918385665</v>
       </c>
     </row>
-    <row r="225" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A225">
         <v>5</v>
       </c>
@@ -37993,7 +37993,7 @@
         <v>31.029096101204967</v>
       </c>
     </row>
-    <row r="226" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A226">
         <v>5</v>
       </c>
@@ -38148,7 +38148,7 @@
         <v>15.034134433109525</v>
       </c>
     </row>
-    <row r="227" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A227">
         <v>5</v>
       </c>
@@ -38303,7 +38303,7 @@
         <v>16.193166923064162</v>
       </c>
     </row>
-    <row r="228" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A228">
         <v>5</v>
       </c>
@@ -38458,7 +38458,7 @@
         <v>66.198496726406205</v>
       </c>
     </row>
-    <row r="229" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A229">
         <v>5</v>
       </c>
@@ -38613,7 +38613,7 @@
         <v>18.950765780398893</v>
       </c>
     </row>
-    <row r="230" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A230">
         <v>5</v>
       </c>
@@ -38768,7 +38768,7 @@
         <v>53.753252547172892</v>
       </c>
     </row>
-    <row r="231" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A231">
         <v>5</v>
       </c>
@@ -38923,7 +38923,7 @@
         <v>17.95273108781803</v>
       </c>
     </row>
-    <row r="232" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A232">
         <v>5</v>
       </c>
@@ -39078,7 +39078,7 @@
         <v>1.634206319258702</v>
       </c>
     </row>
-    <row r="233" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A233">
         <v>5</v>
       </c>
@@ -39233,7 +39233,7 @@
         <v>20.688137399751394</v>
       </c>
     </row>
-    <row r="234" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A234">
         <v>5</v>
       </c>
@@ -39388,7 +39388,7 @@
         <v>30.384162778023253</v>
       </c>
     </row>
-    <row r="235" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I235" s="25" t="s">
         <v>469</v>
       </c>
@@ -39522,7 +39522,7 @@
         <v>28.252942792998947</v>
       </c>
     </row>
-    <row r="236" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A236">
         <v>5</v>
       </c>
@@ -39677,7 +39677,7 @@
         <v>-3.0089019234891268</v>
       </c>
     </row>
-    <row r="237" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A237">
         <v>5</v>
       </c>
@@ -39832,7 +39832,7 @@
         <v>57.815553360107685</v>
       </c>
     </row>
-    <row r="238" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A238">
         <v>5</v>
       </c>
@@ -39987,7 +39987,7 @@
         <v>65.687208062810143</v>
       </c>
     </row>
-    <row r="239" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A239">
         <v>5</v>
       </c>
@@ -40142,7 +40142,7 @@
         <v>-4.633283040023084</v>
       </c>
     </row>
-    <row r="240" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A240">
         <v>5</v>
       </c>
@@ -40297,7 +40297,7 @@
         <v>26.451690525446377</v>
       </c>
     </row>
-    <row r="241" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A241">
         <v>5</v>
       </c>
@@ -40452,7 +40452,7 @@
         <v>43.661908292766952</v>
       </c>
     </row>
-    <row r="242" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A242">
         <v>5</v>
       </c>
@@ -40607,7 +40607,7 @@
         <v>12.624351719259241</v>
       </c>
     </row>
-    <row r="243" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A243">
         <v>5</v>
       </c>
@@ -40762,7 +40762,7 @@
         <v>62.060389842455436</v>
       </c>
     </row>
-    <row r="244" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A244">
         <v>5</v>
       </c>
@@ -40917,7 +40917,7 @@
         <v>20.66597172935225</v>
       </c>
     </row>
-    <row r="245" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A245">
         <v>5</v>
       </c>
@@ -41072,7 +41072,7 @@
         <v>5.0315167530978755</v>
       </c>
     </row>
-    <row r="246" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A246">
         <v>5</v>
       </c>
@@ -41227,7 +41227,7 @@
         <v>25.484791558618713</v>
       </c>
     </row>
-    <row r="247" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A247">
         <v>5</v>
       </c>
@@ -41382,7 +41382,7 @@
         <v>20.134633735242602</v>
       </c>
     </row>
-    <row r="248" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I248" s="25" t="s">
         <v>469</v>
       </c>
@@ -41516,7 +41516,7 @@
         <v>28.368657052848523</v>
       </c>
     </row>
-    <row r="249" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A249">
         <v>5</v>
       </c>
@@ -41671,7 +41671,7 @@
         <v>-30.984842620815908</v>
       </c>
     </row>
-    <row r="250" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A250">
         <v>5</v>
       </c>
@@ -41826,7 +41826,7 @@
         <v>83.202717688830589</v>
       </c>
     </row>
-    <row r="251" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A251">
         <v>5</v>
       </c>
@@ -41981,7 +41981,7 @@
         <v>52.616769330842139</v>
       </c>
     </row>
-    <row r="252" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A252">
         <v>5</v>
       </c>
@@ -42136,7 +42136,7 @@
         <v>-39.452784338689369</v>
       </c>
     </row>
-    <row r="253" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A253">
         <v>5</v>
       </c>
@@ -42291,7 +42291,7 @@
         <v>12.846971974278532</v>
       </c>
     </row>
-    <row r="254" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A254">
         <v>6</v>
       </c>
@@ -42449,7 +42449,7 @@
         <v>-0.39268624835830929</v>
       </c>
     </row>
-    <row r="255" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A255">
         <v>6</v>
       </c>
@@ -42607,7 +42607,7 @@
         <v>-10.295699724232055</v>
       </c>
     </row>
-    <row r="256" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A256">
         <v>6</v>
       </c>
@@ -42762,7 +42762,7 @@
         <v>56.798316471582396</v>
       </c>
     </row>
-    <row r="257" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A257">
         <v>6</v>
       </c>
@@ -42917,7 +42917,7 @@
         <v>2.6481708224523888</v>
       </c>
     </row>
-    <row r="258" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A258">
         <v>6</v>
       </c>
@@ -43072,7 +43072,7 @@
         <v>14.114923360653009</v>
       </c>
     </row>
-    <row r="259" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A259">
         <v>6</v>
       </c>
@@ -43230,7 +43230,7 @@
         <v>3.8364444926330954</v>
       </c>
     </row>
-    <row r="260" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A260">
         <v>6</v>
       </c>
@@ -43385,7 +43385,7 @@
         <v>62.353849031397949</v>
       </c>
     </row>
-    <row r="261" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I261" s="25" t="s">
         <v>469</v>
       </c>
@@ -43519,7 +43519,7 @@
         <v>22.713428388188017</v>
       </c>
     </row>
-    <row r="262" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A262">
         <v>6</v>
       </c>
@@ -43677,7 +43677,7 @@
         <v>13.937121750733361</v>
       </c>
     </row>
-    <row r="263" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A263">
         <v>6</v>
       </c>
@@ -43832,7 +43832,7 @@
         <v>21.083863890092314</v>
       </c>
     </row>
-    <row r="264" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A264">
         <v>6</v>
       </c>
@@ -43987,7 +43987,7 @@
         <v>1.6040980210352274</v>
       </c>
     </row>
-    <row r="265" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A265">
         <v>6</v>
       </c>
@@ -44142,7 +44142,7 @@
         <v>116.83977952817725</v>
       </c>
     </row>
-    <row r="266" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A266">
         <v>6</v>
       </c>
@@ -44297,7 +44297,7 @@
         <v>44.798088951303328</v>
       </c>
     </row>
-    <row r="267" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A267">
         <v>6</v>
       </c>
@@ -44452,7 +44452,7 @@
         <v>41.700755168128097</v>
       </c>
     </row>
-    <row r="268" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A268">
         <v>6</v>
       </c>
@@ -44607,7 +44607,7 @@
         <v>23.471851059846394</v>
       </c>
     </row>
-    <row r="269" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A269">
         <v>6</v>
       </c>
@@ -44762,7 +44762,7 @@
         <v>14.595878615502045</v>
       </c>
     </row>
-    <row r="270" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A270">
         <v>6</v>
       </c>
@@ -44917,7 +44917,7 @@
         <v>20.454548480355328</v>
       </c>
     </row>
-    <row r="271" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A271">
         <v>6</v>
       </c>
@@ -45075,7 +45075,7 @@
         <v>141.48101923319612</v>
       </c>
     </row>
-    <row r="272" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A272">
         <v>6</v>
       </c>
@@ -45230,7 +45230,7 @@
         <v>34.766715760867761</v>
       </c>
     </row>
-    <row r="273" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A273">
         <v>6</v>
       </c>
@@ -45385,7 +45385,7 @@
         <v>57.482812693439023</v>
       </c>
     </row>
-    <row r="274" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I274" s="25" t="s">
         <v>469</v>
       </c>
@@ -45519,7 +45519,7 @@
         <v>23.990205682900001</v>
       </c>
     </row>
-    <row r="275" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A275">
         <v>6</v>
       </c>
@@ -45674,7 +45674,7 @@
         <v>85.887697417803551</v>
       </c>
     </row>
-    <row r="276" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A276">
         <v>6</v>
       </c>
@@ -45829,7 +45829,7 @@
         <v>0.36601482878539926</v>
       </c>
     </row>
-    <row r="277" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A277">
         <v>6</v>
       </c>
@@ -45987,7 +45987,7 @@
         <v>10.202736430073855</v>
       </c>
     </row>
-    <row r="278" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A278">
         <v>6</v>
       </c>
@@ -46142,7 +46142,7 @@
         <v>9.1401105730204435</v>
       </c>
     </row>
-    <row r="279" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A279">
         <v>6</v>
       </c>
@@ -46297,7 +46297,7 @@
         <v>-13.127704953059816</v>
       </c>
     </row>
-    <row r="280" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A280">
         <v>6</v>
       </c>
@@ -46452,7 +46452,7 @@
         <v>60.097887069845427</v>
       </c>
     </row>
-    <row r="281" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A281">
         <v>6</v>
       </c>
@@ -46607,7 +46607,7 @@
         <v>21.954929857894712</v>
       </c>
     </row>
-    <row r="282" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A282">
         <v>6</v>
       </c>
@@ -46762,7 +46762,7 @@
         <v>5.6233885447620757</v>
       </c>
     </row>
-    <row r="283" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A283">
         <v>6</v>
       </c>
@@ -46917,7 +46917,7 @@
         <v>19.072790039722509</v>
       </c>
     </row>
-    <row r="284" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A284">
         <v>6</v>
       </c>
@@ -47072,7 +47072,7 @@
         <v>9.6755920247382221</v>
       </c>
     </row>
-    <row r="285" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A285">
         <v>6</v>
       </c>
@@ -47227,7 +47227,7 @@
         <v>-7.9302553790139285</v>
       </c>
     </row>
-    <row r="286" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A286">
         <v>6</v>
       </c>
@@ -47382,7 +47382,7 @@
         <v>46.990823855592723</v>
       </c>
     </row>
-    <row r="287" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="I287" s="25" t="s">
         <v>469</v>
       </c>
@@ -47516,7 +47516,7 @@
         <v>23.911406684400394</v>
       </c>
     </row>
-    <row r="288" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A288">
         <v>6</v>
       </c>
@@ -47671,7 +47671,7 @@
         <v>16.479241666313982</v>
       </c>
     </row>
-    <row r="289" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A289">
         <v>6</v>
       </c>
@@ -47826,7 +47826,7 @@
         <v>-2.7212487460914758</v>
       </c>
     </row>
-    <row r="290" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A290">
         <v>6</v>
       </c>
@@ -47981,7 +47981,7 @@
         <v>15.213271280793972</v>
       </c>
     </row>
-    <row r="291" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A291">
         <v>6</v>
       </c>
@@ -48136,7 +48136,7 @@
         <v>14.899978774958189</v>
       </c>
     </row>
-    <row r="292" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A292">
         <v>6</v>
       </c>
@@ -48291,7 +48291,7 @@
         <v>10.900371856668034</v>
       </c>
     </row>
-    <row r="293" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A293">
         <v>6</v>
       </c>
@@ -48446,7 +48446,7 @@
         <v>15.144731970386793</v>
       </c>
     </row>
-    <row r="294" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A294">
         <v>6</v>
       </c>
@@ -48601,7 +48601,7 @@
         <v>7.2233405401389552</v>
       </c>
     </row>
-    <row r="295" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A295">
         <v>6</v>
       </c>
@@ -48756,7 +48756,7 @@
         <v>-2.2736211230101055</v>
       </c>
     </row>
-    <row r="296" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A296">
         <v>6</v>
       </c>
@@ -48911,7 +48911,7 @@
         <v>22.976294425758326</v>
       </c>
     </row>
-    <row r="297" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A297">
         <v>6</v>
       </c>
@@ -49066,7 +49066,7 @@
         <v>17.191448139026733</v>
       </c>
     </row>
-    <row r="298" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A298">
         <v>6</v>
       </c>
@@ -49221,7 +49221,7 @@
         <v>-1.248599842509357</v>
       </c>
     </row>
-    <row r="299" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A299">
         <v>6</v>
       </c>
@@ -49376,7 +49376,7 @@
         <v>68.450233700250166</v>
       </c>
     </row>
-    <row r="300" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A300">
         <v>6</v>
       </c>
@@ -49531,7 +49531,7 @@
         <v>26.04657609005967</v>
       </c>
     </row>
-    <row r="301" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A301">
         <v>6</v>
       </c>
@@ -49686,7 +49686,7 @@
         <v>3.5940105932064093</v>
       </c>
     </row>
-    <row r="302" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:52" ht="18" x14ac:dyDescent="0.4">
       <c r="A302">
         <v>6</v>
       </c>
@@ -49841,7 +49841,7 @@
         <v>13.537966303087678</v>
       </c>
     </row>
-    <row r="303" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="F303" s="9"/>
       <c r="I303" s="25" t="s">
         <v>469</v>
@@ -49937,7 +49937,7 @@
       <c r="AY303" s="156"/>
       <c r="AZ303" s="156"/>
     </row>
-    <row r="304" spans="1:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I304" s="25" t="s">
         <v>469</v>
       </c>
@@ -50032,7 +50032,7 @@
       <c r="AY304" s="156"/>
       <c r="AZ304" s="156"/>
     </row>
-    <row r="305" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="305" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I305" s="25" t="s">
         <v>469</v>
       </c>
@@ -50127,7 +50127,7 @@
       <c r="AY305" s="156"/>
       <c r="AZ305" s="156"/>
     </row>
-    <row r="306" spans="9:52" x14ac:dyDescent="0.25">
+    <row r="306" spans="9:52" x14ac:dyDescent="0.35">
       <c r="I306" s="25" t="s">
         <v>469</v>
       </c>
@@ -50146,7 +50146,7 @@
       <c r="AB306" s="23"/>
       <c r="AC306" s="23"/>
     </row>
-    <row r="307" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="307" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I307" s="25" t="s">
         <v>469</v>
       </c>
@@ -50228,7 +50228,7 @@
         <v>-26.03</v>
       </c>
     </row>
-    <row r="308" spans="9:52" x14ac:dyDescent="0.25">
+    <row r="308" spans="9:52" x14ac:dyDescent="0.35">
       <c r="I308" s="25" t="s">
         <v>469</v>
       </c>
@@ -50247,7 +50247,7 @@
       <c r="AB308" s="23"/>
       <c r="AC308" s="23"/>
     </row>
-    <row r="309" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="309" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I309" s="25" t="s">
         <v>469</v>
       </c>
@@ -50328,7 +50328,7 @@
         <v>-27.668419673047392</v>
       </c>
     </row>
-    <row r="310" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="310" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I310" s="25" t="s">
         <v>469</v>
       </c>
@@ -50409,7 +50409,7 @@
         <v>-27.60869166200407</v>
       </c>
     </row>
-    <row r="311" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="311" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I311" s="25" t="s">
         <v>469</v>
       </c>
@@ -50490,7 +50490,7 @@
         <v>-27.638661960653465</v>
       </c>
     </row>
-    <row r="312" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="312" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I312" s="25" t="s">
         <v>469</v>
       </c>
@@ -50571,7 +50571,7 @@
         <v>-27.522115078257109</v>
       </c>
     </row>
-    <row r="313" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="313" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I313" s="25" t="s">
         <v>469</v>
       </c>
@@ -50652,7 +50652,7 @@
         <v>-27.727430701289101</v>
       </c>
     </row>
-    <row r="314" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="314" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I314" s="25" t="s">
         <v>469</v>
       </c>
@@ -50733,7 +50733,7 @@
         <v>-27.742935371963391</v>
       </c>
     </row>
-    <row r="315" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="315" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I315" s="25" t="s">
         <v>469</v>
       </c>
@@ -50814,7 +50814,7 @@
         <v>-27.43730593934178</v>
       </c>
     </row>
-    <row r="316" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="316" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I316" s="25" t="s">
         <v>469</v>
       </c>
@@ -50842,7 +50842,7 @@
       <c r="AK316" s="22"/>
       <c r="AL316" s="22"/>
     </row>
-    <row r="317" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="317" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I317" s="25" t="s">
         <v>469</v>
       </c>
@@ -50924,7 +50924,7 @@
         <v>-26.03</v>
       </c>
     </row>
-    <row r="318" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="318" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I318" s="25" t="s">
         <v>469</v>
       </c>
@@ -50952,7 +50952,7 @@
       <c r="AK318" s="22"/>
       <c r="AL318" s="22"/>
     </row>
-    <row r="319" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="319" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I319" s="25" t="s">
         <v>469</v>
       </c>
@@ -51033,7 +51033,7 @@
         <v>-25.658188394827619</v>
       </c>
     </row>
-    <row r="320" spans="9:52" ht="18" x14ac:dyDescent="0.25">
+    <row r="320" spans="9:52" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I320" s="25" t="s">
         <v>469</v>
       </c>
@@ -51114,7 +51114,7 @@
         <v>-25.844282295845815</v>
       </c>
     </row>
-    <row r="321" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="321" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I321" s="25" t="s">
         <v>469</v>
       </c>
@@ -51195,7 +51195,7 @@
         <v>-26.732262716203572</v>
       </c>
     </row>
-    <row r="322" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="322" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I322" s="25" t="s">
         <v>469</v>
       </c>
@@ -51276,7 +51276,7 @@
         <v>-27.543276373684371</v>
       </c>
     </row>
-    <row r="323" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="323" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I323" s="25" t="s">
         <v>469</v>
       </c>
@@ -51357,7 +51357,7 @@
         <v>-27.03188566587697</v>
       </c>
     </row>
-    <row r="324" spans="9:38" x14ac:dyDescent="0.25">
+    <row r="324" spans="9:38" x14ac:dyDescent="0.35">
       <c r="I324" s="25" t="s">
         <v>469</v>
       </c>
@@ -51381,7 +51381,7 @@
       <c r="AK324" s="23"/>
       <c r="AL324" s="23"/>
     </row>
-    <row r="325" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="325" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I325" s="25" t="s">
         <v>469</v>
       </c>
@@ -51463,7 +51463,7 @@
         <v>-26.03</v>
       </c>
     </row>
-    <row r="326" spans="9:38" x14ac:dyDescent="0.25">
+    <row r="326" spans="9:38" x14ac:dyDescent="0.35">
       <c r="I326" s="25" t="s">
         <v>469</v>
       </c>
@@ -51487,7 +51487,7 @@
       <c r="AK326" s="23"/>
       <c r="AL326" s="23"/>
     </row>
-    <row r="327" spans="9:38" x14ac:dyDescent="0.25">
+    <row r="327" spans="9:38" x14ac:dyDescent="0.35">
       <c r="I327" s="25" t="s">
         <v>469</v>
       </c>
@@ -51511,7 +51511,7 @@
       <c r="AK327" s="23"/>
       <c r="AL327" s="23"/>
     </row>
-    <row r="328" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="328" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I328" s="25" t="s">
         <v>469</v>
       </c>
@@ -51592,7 +51592,7 @@
         <v>-24.907989242213851</v>
       </c>
     </row>
-    <row r="329" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="329" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I329" s="25" t="s">
         <v>469</v>
       </c>
@@ -51673,7 +51673,7 @@
         <v>-24.96289596164684</v>
       </c>
     </row>
-    <row r="330" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="330" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I330" s="25" t="s">
         <v>469</v>
       </c>
@@ -51754,7 +51754,7 @@
         <v>-24.95237166345294</v>
       </c>
     </row>
-    <row r="331" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="331" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I331" s="25" t="s">
         <v>469</v>
       </c>
@@ -51835,7 +51835,7 @@
         <v>-25.466716045859279</v>
       </c>
     </row>
-    <row r="332" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="332" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I332" s="25" t="s">
         <v>469</v>
       </c>
@@ -51916,7 +51916,7 @@
         <v>-25.350593363426174</v>
       </c>
     </row>
-    <row r="333" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="333" spans="9:38" ht="17.5" x14ac:dyDescent="0.35">
       <c r="I333" s="25" t="s">
         <v>469</v>
       </c>
@@ -51997,7 +51997,7 @@
         <v>-25.35776012790301</v>
       </c>
     </row>
-    <row r="334" spans="9:38" x14ac:dyDescent="0.25">
+    <row r="334" spans="9:38" x14ac:dyDescent="0.35">
       <c r="I334" s="25" t="s">
         <v>469</v>
       </c>
@@ -52016,7 +52016,7 @@
       <c r="AB334" s="23"/>
       <c r="AC334" s="23"/>
     </row>
-    <row r="335" spans="9:38" ht="18" x14ac:dyDescent="0.25">
+    <row r="335" spans="9:38" ht="18" x14ac:dyDescent="0.4">
       <c r="I335" s="25" t="s">
         <v>469</v>
       </c>
@@ -52108,9 +52108,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{177815B2-0080-429A-9809-3405254D92C7}">
   <dimension ref="A1:P51"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" ht="22.5" x14ac:dyDescent="0.45">
       <c r="A1" s="35" t="s">
         <v>470</v>
       </c>
@@ -52132,7 +52132,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="14"/>
       <c r="B2" s="14"/>
       <c r="C2" s="14"/>
@@ -52154,7 +52154,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>472</v>
       </c>
@@ -52176,7 +52176,7 @@
         <v>-26.998600937651158</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -52196,7 +52196,7 @@
         <v>-26.919940780647767</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>473</v>
       </c>
@@ -52220,7 +52220,7 @@
         <v>-28.505475833017826</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>474</v>
       </c>
@@ -52244,7 +52244,7 @@
         <v>-26.364614246438375</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="14"/>
       <c r="B7" s="14"/>
       <c r="C7" s="14"/>
@@ -52266,7 +52266,7 @@
         <v>-27.795870405601409</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="14"/>
       <c r="B8" s="39" t="s">
         <v>476</v>
@@ -52292,7 +52292,7 @@
         <v>-26.709177173545527</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="14"/>
       <c r="B9" s="43" t="s">
         <v>477</v>
@@ -52324,7 +52324,7 @@
         <v>-27.729330844125514</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="14"/>
       <c r="B10" s="45" t="s">
         <v>479</v>
@@ -52362,7 +52362,7 @@
         <v>-26.370139322061156</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="14"/>
       <c r="B11" s="48">
         <v>-8</v>
@@ -52401,7 +52401,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>480</v>
       </c>
@@ -52443,7 +52443,7 @@
         <v>-27.935029930251016</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>481</v>
       </c>
@@ -52485,7 +52485,7 @@
         <v>-25.100908062892564</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14" s="14"/>
       <c r="B14" s="50">
         <v>-5</v>
@@ -52525,7 +52525,7 @@
         <v>-27.133739107563105</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="14"/>
       <c r="B15" s="12">
         <v>-2.6581644588492788</v>
@@ -52555,7 +52555,7 @@
         <v>-26.608784761803804</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="14"/>
       <c r="B16" s="12">
         <v>-1.2689927303572093</v>
@@ -52585,7 +52585,7 @@
         <v>-27.046137223050184</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="14"/>
       <c r="B17" s="12">
         <v>-5.4894210892118593</v>
@@ -52615,7 +52615,7 @@
         <v>-26.61790613380245</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="57"/>
       <c r="B18" s="12">
         <v>-5.1643423896774925</v>
@@ -52643,7 +52643,7 @@
         <v>-28.255602976398894</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="57"/>
       <c r="B19" s="61">
         <v>-3.7993147467586903</v>
@@ -52673,7 +52673,7 @@
         <v>-25.7165414932375</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="14"/>
       <c r="B20" s="61">
         <v>-2.004370675907571</v>
@@ -52703,7 +52703,7 @@
         <v>-27.074798716117325</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="14"/>
       <c r="B21" s="12">
         <v>-3.1789297141235893</v>
@@ -52732,7 +52732,7 @@
         <v>-26.95152997901387</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="14"/>
       <c r="B22" s="61">
         <v>-2.4742540961763702</v>
@@ -52762,7 +52762,7 @@
         <v>-28.264215175037467</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="14"/>
       <c r="B23" s="48">
         <v>4</v>
@@ -52792,7 +52792,7 @@
         <v>-26.451194935231044</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="77"/>
       <c r="B24" s="78">
         <v>1.0397630667569111</v>
@@ -52821,7 +52821,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="91" t="s">
         <v>496</v>
       </c>
@@ -52852,7 +52852,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="14"/>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -52872,7 +52872,7 @@
         <v>-29.806406579286122</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="18" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="17.5" x14ac:dyDescent="0.35">
       <c r="A27" s="81" t="s">
         <v>482</v>
       </c>
@@ -52894,7 +52894,7 @@
         <v>-30.388567716176009</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="23.25" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" ht="22.5" x14ac:dyDescent="0.45">
       <c r="A28" s="83"/>
       <c r="B28" s="82"/>
       <c r="C28" s="82"/>
@@ -52914,7 +52914,7 @@
         <v>-29.000224244194584</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29" s="82"/>
       <c r="B29" s="84" t="s">
         <v>483</v>
@@ -52942,7 +52942,7 @@
         <v>-28.409641159746062</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="82"/>
       <c r="B30" s="84"/>
       <c r="C30" s="82"/>
@@ -52962,7 +52962,7 @@
         <v>-28.92468759162638</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A31" s="82"/>
       <c r="B31" s="82"/>
       <c r="C31" s="82"/>
@@ -52982,7 +52982,7 @@
         <v>-26.587436575322588</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A32" s="82"/>
       <c r="B32" s="82"/>
       <c r="C32" s="85" t="s">
@@ -53020,7 +53020,7 @@
         <v>-29.317790908933283</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A33" s="82"/>
       <c r="B33" s="82"/>
       <c r="C33" s="87">
@@ -53063,7 +53063,7 @@
         <v>-29.584145375992176</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N34" s="93">
         <v>-0.57367924872246234</v>
       </c>
@@ -53071,7 +53071,7 @@
         <v>-28.911913952832347</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N35" s="93">
         <v>-1.5662041363964359</v>
       </c>
@@ -53079,7 +53079,7 @@
         <v>-29.183498569990306</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N36" s="93">
         <v>2.6359327048377388</v>
       </c>
@@ -53087,7 +53087,7 @@
         <v>-28.695901283257431</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N37" s="93">
         <v>3.7916853602788558</v>
       </c>
@@ -53095,14 +53095,14 @@
         <v>-26.982676741060146</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N38" s="93"/>
       <c r="O38" s="93"/>
       <c r="P38" s="25" t="s">
         <v>469</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N39" s="93">
         <v>-0.61572461110105225</v>
       </c>
@@ -53110,7 +53110,7 @@
         <v>-30.556804534032352</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N40" s="93">
         <v>-3.6030142064232393</v>
       </c>
@@ -53118,7 +53118,7 @@
         <v>-30.579366609566662</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N41" s="93">
         <v>-1.2566769119879622</v>
       </c>
@@ -53126,7 +53126,7 @@
         <v>-29.571735057907052</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N42" s="94">
         <v>-2.5413004979459872</v>
       </c>
@@ -53134,7 +53134,7 @@
         <v>-30.181838126035053</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N43" s="94">
         <v>-1.1688176210412387</v>
       </c>
@@ -53142,7 +53142,7 @@
         <v>-29.494021835189361</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N44" s="94">
         <v>-0.66996516800450323</v>
       </c>
@@ -53150,7 +53150,7 @@
         <v>-30.273955014687434</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N45" s="94">
         <v>-0.82413221891652733</v>
       </c>
@@ -53158,7 +53158,7 @@
         <v>-30.071069955843111</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N46" s="94">
         <v>0.17732331492664621</v>
       </c>
@@ -53166,7 +53166,7 @@
         <v>-29.402051774330886</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N47" s="94">
         <v>3.7254070841054245</v>
       </c>
@@ -53174,7 +53174,7 @@
         <v>-28.182626671666171</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
       <c r="N48" s="93">
         <v>0.76826046575739382</v>
       </c>
@@ -53182,7 +53182,7 @@
         <v>-28.718911845055686</v>
       </c>
     </row>
-    <row r="49" spans="13:15" x14ac:dyDescent="0.25">
+    <row r="49" spans="13:15" x14ac:dyDescent="0.35">
       <c r="N49" s="93">
         <v>4.4518425702024791</v>
       </c>
@@ -53190,11 +53190,11 @@
         <v>-26.965048333365136</v>
       </c>
     </row>
-    <row r="50" spans="13:15" x14ac:dyDescent="0.25">
+    <row r="50" spans="13:15" x14ac:dyDescent="0.35">
       <c r="N50" s="92"/>
       <c r="O50" s="92"/>
     </row>
-    <row r="51" spans="13:15" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="13:15" ht="18.5" x14ac:dyDescent="0.45">
       <c r="M51" s="95" t="s">
         <v>497</v>
       </c>
@@ -53216,37 +53216,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C304031-B527-4D03-ABED-2C4396F5251E}">
   <dimension ref="A1:AB303"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="6.5703125" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" customWidth="1"/>
-    <col min="3" max="3" width="11.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" customWidth="1"/>
-    <col min="6" max="6" width="7.7109375" customWidth="1"/>
-    <col min="7" max="7" width="8.42578125" customWidth="1"/>
-    <col min="8" max="8" width="9.7109375" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" customWidth="1"/>
-    <col min="10" max="10" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.54296875" customWidth="1"/>
+    <col min="2" max="2" width="7.7265625" customWidth="1"/>
+    <col min="3" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" customWidth="1"/>
+    <col min="6" max="6" width="7.7265625" customWidth="1"/>
+    <col min="7" max="7" width="8.453125" customWidth="1"/>
+    <col min="8" max="8" width="9.7265625" customWidth="1"/>
+    <col min="9" max="9" width="9.54296875" customWidth="1"/>
+    <col min="10" max="10" width="21.54296875" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="23" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10" customWidth="1"/>
-    <col min="14" max="14" width="24.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.26953125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.1796875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="22.81640625" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="23" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="25.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="25.81640625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="24.26953125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="21" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.85546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="23.85546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="23.81640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="24.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" s="100" t="s">
         <v>21</v>
       </c>
@@ -53332,7 +53332,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2" s="100"/>
       <c r="B2" s="100"/>
       <c r="C2" s="100"/>
@@ -53390,7 +53390,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A3" s="113">
         <v>1</v>
       </c>
@@ -53476,7 +53476,7 @@
         <v>-5.3244169427735253</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A4" s="113">
         <v>1</v>
       </c>
@@ -53562,7 +53562,7 @@
         <v>7.4762608501921513</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A5" s="113">
         <v>1</v>
       </c>
@@ -53648,7 +53648,7 @@
         <v>6.9952936876060967</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="113">
         <v>1</v>
       </c>
@@ -53734,7 +53734,7 @@
         <v>9.4967314350991057</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7" s="113">
         <v>1</v>
       </c>
@@ -53818,7 +53818,7 @@
         <v>15.365658453763142</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8" s="113">
         <v>1</v>
       </c>
@@ -53902,7 +53902,7 @@
         <v>16.230545780042682</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9" s="113">
         <v>1</v>
       </c>
@@ -53986,7 +53986,7 @@
         <v>-1.2030850909905413</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10" s="113">
         <v>1</v>
       </c>
@@ -54070,7 +54070,7 @@
         <v>22.336451425768455</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11" s="113">
         <v>1</v>
       </c>
@@ -54154,7 +54154,7 @@
         <v>6.5994037387739901</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12" s="113">
         <v>1</v>
       </c>
@@ -54238,7 +54238,7 @@
         <v>18.547934826012025</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13" s="113">
         <v>1</v>
       </c>
@@ -54322,7 +54322,7 @@
         <v>7.3310352709321505</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14" s="113">
         <v>1</v>
       </c>
@@ -54406,7 +54406,7 @@
         <v>22.275702691121335</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15" s="113"/>
       <c r="B15" s="113"/>
       <c r="C15" s="113"/>
@@ -54476,7 +54476,7 @@
         <v>28.132506819327215</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16" s="113">
         <v>1</v>
       </c>
@@ -54560,7 +54560,7 @@
         <v>5.0692805042840128</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A17" s="113">
         <v>1</v>
       </c>
@@ -54644,7 +54644,7 @@
         <v>36.230825698042594</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A18" s="113">
         <v>1</v>
       </c>
@@ -54728,7 +54728,7 @@
         <v>13.879778274190624</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A19" s="113">
         <v>1</v>
       </c>
@@ -54812,7 +54812,7 @@
         <v>19.651766145958316</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A20" s="113">
         <v>1</v>
       </c>
@@ -54896,7 +54896,7 @@
         <v>14.842984840877095</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A21" s="113">
         <v>1</v>
       </c>
@@ -54980,7 +54980,7 @@
         <v>19.551475240464633</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A22" s="113">
         <v>1</v>
       </c>
@@ -55064,7 +55064,7 @@
         <v>1.5444138152065356</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A23" s="113">
         <v>1</v>
       </c>
@@ -55148,7 +55148,7 @@
         <v>29.462021533541719</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A24" s="113">
         <v>1</v>
       </c>
@@ -55232,7 +55232,7 @@
         <v>14.527844129006429</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A25" s="113">
         <v>1</v>
       </c>
@@ -55316,7 +55316,7 @@
         <v>15.883215135659157</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A26" s="113">
         <v>1</v>
       </c>
@@ -55400,7 +55400,7 @@
         <v>1.4497178838301927</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A27" s="113">
         <v>1</v>
       </c>
@@ -55484,7 +55484,7 @@
         <v>21.384487617990278</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A28" s="113"/>
       <c r="B28" s="113"/>
       <c r="C28" s="113"/>
@@ -55554,7 +55554,7 @@
         <v>26.753141026636396</v>
       </c>
     </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A29" s="113"/>
       <c r="B29" s="113"/>
       <c r="C29" s="113"/>
@@ -55624,7 +55624,7 @@
         <v>34.769657483357804</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A30" s="113">
         <v>1</v>
       </c>
@@ -55708,7 +55708,7 @@
         <v>-15.507829776952864</v>
       </c>
     </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A31" s="113">
         <v>1</v>
       </c>
@@ -55792,7 +55792,7 @@
         <v>-21.909277947707029</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A32" s="113">
         <v>1</v>
       </c>
@@ -55876,7 +55876,7 @@
         <v>-6.6431796576416069</v>
       </c>
     </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A33" s="113">
         <v>1</v>
       </c>
@@ -55960,7 +55960,7 @@
         <v>-0.14932473304973826</v>
       </c>
     </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A34" s="113">
         <v>1</v>
       </c>
@@ -56044,7 +56044,7 @@
         <v>-5.8125990255741833</v>
       </c>
     </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A35" s="113">
         <v>1</v>
       </c>
@@ -56128,7 +56128,7 @@
         <v>19.886492701135516</v>
       </c>
     </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A36" s="113">
         <v>1</v>
       </c>
@@ -56212,7 +56212,7 @@
         <v>-10.135072198684814</v>
       </c>
     </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A37" s="113">
         <v>1</v>
       </c>
@@ -56296,7 +56296,7 @@
         <v>-13.063865793820906</v>
       </c>
     </row>
-    <row r="38" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A38" s="113">
         <v>1</v>
       </c>
@@ -56380,7 +56380,7 @@
         <v>-5.6721436809437087</v>
       </c>
     </row>
-    <row r="39" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A39" s="113">
         <v>1</v>
       </c>
@@ -56464,7 +56464,7 @@
         <v>-8.6584204462503145</v>
       </c>
     </row>
-    <row r="40" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A40" s="113">
         <v>1</v>
       </c>
@@ -56548,7 +56548,7 @@
         <v>-3.2969350751255178</v>
       </c>
     </row>
-    <row r="41" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A41" s="113">
         <v>1</v>
       </c>
@@ -56632,7 +56632,7 @@
         <v>15.540748943556613</v>
       </c>
     </row>
-    <row r="42" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A42" s="113"/>
       <c r="B42" s="113"/>
       <c r="C42" s="113"/>
@@ -56702,7 +56702,7 @@
         <v>25.491911714283777</v>
       </c>
     </row>
-    <row r="43" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A43" s="113">
         <v>1</v>
       </c>
@@ -56786,7 +56786,7 @@
         <v>-23.759226673198963</v>
       </c>
     </row>
-    <row r="44" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A44" s="113">
         <v>1</v>
       </c>
@@ -56870,7 +56870,7 @@
         <v>-24.007322018404498</v>
       </c>
     </row>
-    <row r="45" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A45" s="113">
         <v>1</v>
       </c>
@@ -56954,7 +56954,7 @@
         <v>-12.927403420490702</v>
       </c>
     </row>
-    <row r="46" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A46" s="113">
         <v>1</v>
       </c>
@@ -57038,7 +57038,7 @@
         <v>-19.636068357560266</v>
       </c>
     </row>
-    <row r="47" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A47" s="113">
         <v>1</v>
       </c>
@@ -57122,7 +57122,7 @@
         <v>-12.072878974422885</v>
       </c>
     </row>
-    <row r="48" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A48" s="126">
         <v>1</v>
       </c>
@@ -57206,7 +57206,7 @@
         <v>-20.648989283758024</v>
       </c>
     </row>
-    <row r="49" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A49" s="113">
         <v>1</v>
       </c>
@@ -57290,7 +57290,7 @@
         <v>-18.418059953790866</v>
       </c>
     </row>
-    <row r="50" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A50" s="113">
         <v>1</v>
       </c>
@@ -57374,7 +57374,7 @@
         <v>-11.061590105845287</v>
       </c>
     </row>
-    <row r="51" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A51" s="113">
         <v>1</v>
       </c>
@@ -57458,7 +57458,7 @@
         <v>2.346828293546821</v>
       </c>
     </row>
-    <row r="52" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A52" s="113">
         <v>1</v>
       </c>
@@ -57542,7 +57542,7 @@
         <v>-3.5499515637527068</v>
       </c>
     </row>
-    <row r="53" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A53" s="113">
         <v>1</v>
       </c>
@@ -57626,7 +57626,7 @@
         <v>15.734577584693987</v>
       </c>
     </row>
-    <row r="54" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A54" s="126">
         <v>2</v>
       </c>
@@ -57710,7 +57710,7 @@
         <v>16.665139265799045</v>
       </c>
     </row>
-    <row r="55" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A55" s="113"/>
       <c r="B55" s="113"/>
       <c r="C55" s="113"/>
@@ -57780,7 +57780,7 @@
         <v>26.148622239365871</v>
       </c>
     </row>
-    <row r="56" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A56" s="113">
         <v>2</v>
       </c>
@@ -57864,7 +57864,7 @@
         <v>17.784775262652541</v>
       </c>
     </row>
-    <row r="57" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A57" s="113">
         <v>2</v>
       </c>
@@ -57948,7 +57948,7 @@
         <v>15.219048009809111</v>
       </c>
     </row>
-    <row r="58" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A58" s="113">
         <v>2</v>
       </c>
@@ -58032,7 +58032,7 @@
         <v>13.204014021752641</v>
       </c>
     </row>
-    <row r="59" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A59" s="113">
         <v>2</v>
       </c>
@@ -58116,7 +58116,7 @@
         <v>31.787552054489687</v>
       </c>
     </row>
-    <row r="60" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A60" s="113">
         <v>2</v>
       </c>
@@ -58200,7 +58200,7 @@
         <v>35.689587892746566</v>
       </c>
     </row>
-    <row r="61" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A61" s="113">
         <v>2</v>
       </c>
@@ -58284,7 +58284,7 @@
         <v>2.6404056540685339</v>
       </c>
     </row>
-    <row r="62" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A62" s="113">
         <v>2</v>
       </c>
@@ -58368,7 +58368,7 @@
         <v>28.571759230215932</v>
       </c>
     </row>
-    <row r="63" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A63" s="113">
         <v>2</v>
       </c>
@@ -58452,7 +58452,7 @@
         <v>7.9959658469408446</v>
       </c>
     </row>
-    <row r="64" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A64" s="113">
         <v>2</v>
       </c>
@@ -58536,7 +58536,7 @@
         <v>15.791264292464025</v>
       </c>
     </row>
-    <row r="65" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A65" s="113">
         <v>2</v>
       </c>
@@ -58620,7 +58620,7 @@
         <v>10.691756753840043</v>
       </c>
     </row>
-    <row r="66" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A66" s="113">
         <v>2</v>
       </c>
@@ -58704,7 +58704,7 @@
         <v>38.795023880133776</v>
       </c>
     </row>
-    <row r="67" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A67" s="113">
         <v>2</v>
       </c>
@@ -58790,7 +58790,7 @@
         <v>56.515869319642142</v>
       </c>
     </row>
-    <row r="68" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A68" s="113"/>
       <c r="B68" s="113"/>
       <c r="C68" s="113"/>
@@ -58860,7 +58860,7 @@
         <v>25.819098391024475</v>
       </c>
     </row>
-    <row r="69" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A69" s="113">
         <v>2</v>
       </c>
@@ -58946,7 +58946,7 @@
         <v>60.351715928450567</v>
       </c>
     </row>
-    <row r="70" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A70" s="113">
         <v>2</v>
       </c>
@@ -59032,7 +59032,7 @@
         <v>3.9733385842177782</v>
       </c>
     </row>
-    <row r="71" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A71" s="113">
         <v>2</v>
       </c>
@@ -59116,7 +59116,7 @@
         <v>15.078548008766735</v>
       </c>
     </row>
-    <row r="72" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A72" s="113">
         <v>2</v>
       </c>
@@ -59200,7 +59200,7 @@
         <v>17.384242332534328</v>
       </c>
     </row>
-    <row r="73" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A73" s="113">
         <v>2</v>
       </c>
@@ -59284,7 +59284,7 @@
         <v>26.346655837266031</v>
       </c>
     </row>
-    <row r="74" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A74" s="113">
         <v>2</v>
       </c>
@@ -59368,7 +59368,7 @@
         <v>37.853197091921587</v>
       </c>
     </row>
-    <row r="75" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A75" s="113">
         <v>2</v>
       </c>
@@ -59452,7 +59452,7 @@
         <v>25.766690211803667</v>
       </c>
     </row>
-    <row r="76" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A76" s="113">
         <v>2</v>
       </c>
@@ -59536,7 +59536,7 @@
         <v>11.96095688313692</v>
       </c>
     </row>
-    <row r="77" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A77" s="113">
         <v>2</v>
       </c>
@@ -59620,7 +59620,7 @@
         <v>12.65975719979995</v>
       </c>
     </row>
-    <row r="78" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A78" s="113">
         <v>2</v>
       </c>
@@ -59704,7 +59704,7 @@
         <v>25.831534669980005</v>
       </c>
     </row>
-    <row r="79" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A79" s="113">
         <v>2</v>
       </c>
@@ -59788,7 +59788,7 @@
         <v>9.1466401525552854</v>
       </c>
     </row>
-    <row r="80" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A80" s="113">
         <v>2</v>
       </c>
@@ -59872,7 +59872,7 @@
         <v>16.068377852402893</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A81" s="113"/>
       <c r="B81" s="113"/>
       <c r="C81" s="113"/>
@@ -59942,7 +59942,7 @@
         <v>27.100531742443312</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A82" s="113">
         <v>2</v>
       </c>
@@ -60026,7 +60026,7 @@
         <v>25.961303582526796</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A83" s="113">
         <v>2</v>
       </c>
@@ -60110,7 +60110,7 @@
         <v>7.194066647853159</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A84" s="113">
         <v>2</v>
       </c>
@@ -60194,7 +60194,7 @@
         <v>18.491210485580556</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A85" s="113">
         <v>2</v>
       </c>
@@ -60278,7 +60278,7 @@
         <v>10.847211045783567</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A86" s="113">
         <v>2</v>
       </c>
@@ -60362,7 +60362,7 @@
         <v>-8.078925738081999</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A87" s="113">
         <v>2</v>
       </c>
@@ -60446,7 +60446,7 @@
         <v>62.004772727035636</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A88" s="113">
         <v>2</v>
       </c>
@@ -60530,7 +60530,7 @@
         <v>42.820314867457739</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A89" s="113">
         <v>2</v>
       </c>
@@ -60614,7 +60614,7 @@
         <v>16.259930706703507</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A90" s="113">
         <v>2</v>
       </c>
@@ -60698,7 +60698,7 @@
         <v>23.376634584646446</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A91" s="113">
         <v>2</v>
       </c>
@@ -60782,7 +60782,7 @@
         <v>13.905410430545828</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A92" s="113">
         <v>2</v>
       </c>
@@ -60866,7 +60866,7 @@
         <v>19.102495323024549</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A93" s="113">
         <v>2</v>
       </c>
@@ -60950,7 +60950,7 @@
         <v>22.98579685527713</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A94" s="113"/>
       <c r="B94" s="113"/>
       <c r="C94" s="113"/>
@@ -61020,7 +61020,7 @@
         <v>24.843083571290947</v>
       </c>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A95" s="113">
         <v>2</v>
       </c>
@@ -61104,7 +61104,7 @@
         <v>25.295615915854608</v>
       </c>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A96" s="113">
         <v>2</v>
       </c>
@@ -61188,7 +61188,7 @@
         <v>-4.0183883665156905</v>
       </c>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A97" s="113">
         <v>2</v>
       </c>
@@ -61272,7 +61272,7 @@
         <v>13.620583672548925</v>
       </c>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A98" s="113">
         <v>2</v>
       </c>
@@ -61356,7 +61356,7 @@
         <v>40.800081165197625</v>
       </c>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A99" s="113">
         <v>2</v>
       </c>
@@ -61440,7 +61440,7 @@
         <v>29.972927722388132</v>
       </c>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A100" s="113">
         <v>2</v>
       </c>
@@ -61524,7 +61524,7 @@
         <v>7.9488463025767508</v>
       </c>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A101" s="113">
         <v>2</v>
       </c>
@@ -61608,7 +61608,7 @@
         <v>3.7869454832883953</v>
       </c>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A102" s="113">
         <v>2</v>
       </c>
@@ -61692,7 +61692,7 @@
         <v>7.4003659563848245</v>
       </c>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A103" s="113">
         <v>2</v>
       </c>
@@ -61776,7 +61776,7 @@
         <v>14.696366506086189</v>
       </c>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A104" s="113">
         <v>3</v>
       </c>
@@ -61860,7 +61860,7 @@
         <v>62.48543473915236</v>
       </c>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A105" s="113">
         <v>3</v>
       </c>
@@ -61944,7 +61944,7 @@
         <v>37.516290895776017</v>
       </c>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A106" s="113">
         <v>3</v>
       </c>
@@ -62028,7 +62028,7 @@
         <v>7.593533834717725</v>
       </c>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A107" s="113"/>
       <c r="B107" s="113"/>
       <c r="C107" s="113"/>
@@ -62098,7 +62098,7 @@
         <v>24.672609080109709</v>
       </c>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A108" s="113">
         <v>3</v>
       </c>
@@ -62182,7 +62182,7 @@
         <v>15.461977886515042</v>
       </c>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A109" s="113">
         <v>3</v>
       </c>
@@ -62266,7 +62266,7 @@
         <v>7.284794607489431</v>
       </c>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A110" s="113">
         <v>3</v>
       </c>
@@ -62350,7 +62350,7 @@
         <v>11.580366855012958</v>
       </c>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A111" s="113">
         <v>3</v>
       </c>
@@ -62434,7 +62434,7 @@
         <v>95.367712532918873</v>
       </c>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A112" s="113">
         <v>3</v>
       </c>
@@ -62518,7 +62518,7 @@
         <v>66.692618718555693</v>
       </c>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A113" s="113">
         <v>3</v>
       </c>
@@ -62602,7 +62602,7 @@
         <v>55.754802496730264</v>
       </c>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A114" s="113">
         <v>3</v>
       </c>
@@ -62686,7 +62686,7 @@
         <v>29.131015973142826</v>
       </c>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A115" s="113">
         <v>3</v>
       </c>
@@ -62770,7 +62770,7 @@
         <v>4.9783064151820442</v>
       </c>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A116" s="113">
         <v>3</v>
       </c>
@@ -62854,7 +62854,7 @@
         <v>17.947699343838774</v>
       </c>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A117" s="113">
         <v>3</v>
       </c>
@@ -62938,7 +62938,7 @@
         <v>92.55704934699294</v>
       </c>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A118" s="113">
         <v>3</v>
       </c>
@@ -63022,7 +63022,7 @@
         <v>55.065776228873098</v>
       </c>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A119" s="113">
         <v>3</v>
       </c>
@@ -63106,7 +63106,7 @@
         <v>19.417202740654727</v>
       </c>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A120" s="113"/>
       <c r="B120" s="113"/>
       <c r="C120" s="113"/>
@@ -63176,7 +63176,7 @@
         <v>28.033006413941131</v>
       </c>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A121" s="113">
         <v>3</v>
       </c>
@@ -63260,7 +63260,7 @@
         <v>20.758755722840583</v>
       </c>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A122" s="113">
         <v>3</v>
       </c>
@@ -63344,7 +63344,7 @@
         <v>13.351083420030108</v>
       </c>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A123" s="113">
         <v>3</v>
       </c>
@@ -63428,7 +63428,7 @@
         <v>21.001449417599183</v>
       </c>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A124" s="113">
         <v>3</v>
       </c>
@@ -63512,7 +63512,7 @@
         <v>13.702955888494905</v>
       </c>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A125" s="113">
         <v>3</v>
       </c>
@@ -63596,7 +63596,7 @@
         <v>3.548073118524453</v>
       </c>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A126" s="113">
         <v>3</v>
       </c>
@@ -63680,7 +63680,7 @@
         <v>31.301592136399048</v>
       </c>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A127" s="113">
         <v>3</v>
       </c>
@@ -63764,7 +63764,7 @@
         <v>27.89330917031041</v>
       </c>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A128" s="113">
         <v>3</v>
       </c>
@@ -63848,7 +63848,7 @@
         <v>12.606275150597313</v>
       </c>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A129" s="113">
         <v>3</v>
       </c>
@@ -63932,7 +63932,7 @@
         <v>27.020042077479101</v>
       </c>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A130" s="113">
         <v>3</v>
       </c>
@@ -64016,7 +64016,7 @@
         <v>14.906319833334347</v>
       </c>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A131" s="113">
         <v>3</v>
       </c>
@@ -64100,7 +64100,7 @@
         <v>8.4947505373578203</v>
       </c>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A132" s="113">
         <v>3</v>
       </c>
@@ -64184,7 +64184,7 @@
         <v>64.219490858574702</v>
       </c>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A133" s="113"/>
       <c r="B133" s="113"/>
       <c r="C133" s="113"/>
@@ -64254,7 +64254,7 @@
         <v>35.952643870333922</v>
       </c>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A134" s="113">
         <v>3</v>
       </c>
@@ -64338,7 +64338,7 @@
         <v>34.74466443351254</v>
       </c>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A135" s="113">
         <v>3</v>
       </c>
@@ -64422,7 +64422,7 @@
         <v>1.8530535675331805</v>
       </c>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A136" s="113">
         <v>3</v>
       </c>
@@ -64506,7 +64506,7 @@
         <v>31.109090383014681</v>
       </c>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A137" s="113">
         <v>3</v>
       </c>
@@ -64590,7 +64590,7 @@
         <v>29.958957031468444</v>
       </c>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A138" s="113">
         <v>3</v>
       </c>
@@ -64676,7 +64676,7 @@
         <v>-1.6848069852248848</v>
       </c>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A139" s="113">
         <v>3</v>
       </c>
@@ -64760,7 +64760,7 @@
         <v>53.919571607328187</v>
       </c>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A140" s="113">
         <v>3</v>
       </c>
@@ -64844,7 +64844,7 @@
         <v>42.76664463077617</v>
       </c>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A141" s="113">
         <v>3</v>
       </c>
@@ -64928,7 +64928,7 @@
         <v>15.59378725067395</v>
       </c>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A142" s="113">
         <v>3</v>
       </c>
@@ -65012,7 +65012,7 @@
         <v>30.533660363714077</v>
       </c>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A143" s="113">
         <v>3</v>
       </c>
@@ -65096,7 +65096,7 @@
         <v>62.281562868100607</v>
       </c>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A144" s="113">
         <v>3</v>
       </c>
@@ -65180,7 +65180,7 @@
         <v>22.778575429192038</v>
       </c>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A145" s="113">
         <v>3</v>
       </c>
@@ -65264,7 +65264,7 @@
         <v>79.094266030972364</v>
       </c>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A146" s="113"/>
       <c r="B146" s="113"/>
       <c r="C146" s="113"/>
@@ -65334,7 +65334,7 @@
         <v>33.906575862074902</v>
       </c>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A147" s="113">
         <v>3</v>
       </c>
@@ -65418,7 +65418,7 @@
         <v>36.208827759443011</v>
       </c>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A148" s="113">
         <v>3</v>
       </c>
@@ -65504,7 +65504,7 @@
         <v>29.869769544870195</v>
       </c>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A149" s="113">
         <v>3</v>
       </c>
@@ -65590,7 +65590,7 @@
         <v>21.930998657144762</v>
       </c>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A150" s="113">
         <v>3</v>
       </c>
@@ -65674,7 +65674,7 @@
         <v>52.12235231520701</v>
       </c>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A151" s="113">
         <v>3</v>
       </c>
@@ -65758,7 +65758,7 @@
         <v>26.265788860289074</v>
       </c>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A152" s="113">
         <v>3</v>
       </c>
@@ -65842,7 +65842,7 @@
         <v>5.8240903822071033</v>
       </c>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A153" s="113">
         <v>3</v>
       </c>
@@ -65926,7 +65926,7 @@
         <v>26.619707997799221</v>
       </c>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A154" s="113">
         <v>3</v>
       </c>
@@ -66012,7 +66012,7 @@
         <v>-9.6967820917170933</v>
       </c>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A155" s="113">
         <v>3</v>
       </c>
@@ -66096,7 +66096,7 @@
         <v>24.669646815347335</v>
       </c>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A156" s="113">
         <v>4</v>
       </c>
@@ -66180,7 +66180,7 @@
         <v>26.674970205766702</v>
       </c>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A157" s="113">
         <v>4</v>
       </c>
@@ -66264,7 +66264,7 @@
         <v>32.287692062091807</v>
       </c>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A158" s="113">
         <v>4</v>
       </c>
@@ -66348,7 +66348,7 @@
         <v>50.619765852664145</v>
       </c>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A159" s="113"/>
       <c r="B159" s="113"/>
       <c r="C159" s="113"/>
@@ -66418,7 +66418,7 @@
         <v>24.143278885555564</v>
       </c>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A160" s="113">
         <v>4</v>
       </c>
@@ -66502,7 +66502,7 @@
         <v>20.878184364225838</v>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A161" s="113">
         <v>4</v>
       </c>
@@ -66586,7 +66586,7 @@
         <v>10.026673133636255</v>
       </c>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A162" s="113">
         <v>4</v>
       </c>
@@ -66670,7 +66670,7 @@
         <v>12.623962319338045</v>
       </c>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A163" s="113">
         <v>4</v>
       </c>
@@ -66754,7 +66754,7 @@
         <v>35.762960912166797</v>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A164" s="113">
         <v>4</v>
       </c>
@@ -66838,7 +66838,7 @@
         <v>54.571596856574089</v>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A165" s="113">
         <v>4</v>
       </c>
@@ -66922,7 +66922,7 @@
         <v>16.777771244318451</v>
       </c>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A166" s="113">
         <v>4</v>
       </c>
@@ -67006,7 +67006,7 @@
         <v>21.510498700969549</v>
       </c>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A167" s="113">
         <v>4</v>
       </c>
@@ -67090,7 +67090,7 @@
         <v>4.1038166686657718</v>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A168" s="113">
         <v>4</v>
       </c>
@@ -67174,7 +67174,7 @@
         <v>16.153326373478105</v>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A169" s="113">
         <v>4</v>
       </c>
@@ -67258,7 +67258,7 @@
         <v>47.96002314238379</v>
       </c>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A170" s="113">
         <v>4</v>
       </c>
@@ -67342,7 +67342,7 @@
         <v>54.15353403719125</v>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A171" s="113">
         <v>4</v>
       </c>
@@ -67426,7 +67426,7 @@
         <v>30.806284326871939</v>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A172" s="113">
         <v>4</v>
       </c>
@@ -67510,7 +67510,7 @@
         <v>118.75181611487263</v>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A173" s="113">
         <v>4</v>
       </c>
@@ -67594,7 +67594,7 @@
         <v>15.018254519700847</v>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A174" s="113">
         <v>4</v>
       </c>
@@ -67678,7 +67678,7 @@
         <v>23.737368401932635</v>
       </c>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A175" s="113">
         <v>4</v>
       </c>
@@ -67762,7 +67762,7 @@
         <v>4.030757731496859</v>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A176" s="113">
         <v>4</v>
       </c>
@@ -67846,7 +67846,7 @@
         <v>30.182071919533371</v>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A177" s="113">
         <v>4</v>
       </c>
@@ -67930,7 +67930,7 @@
         <v>27.804072438022409</v>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A178" s="113">
         <v>4</v>
       </c>
@@ -68014,7 +68014,7 @@
         <v>69.012767176126474</v>
       </c>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A179" s="113">
         <v>4</v>
       </c>
@@ -68098,7 +68098,7 @@
         <v>24.131627899157682</v>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A180" s="113">
         <v>4</v>
       </c>
@@ -68182,7 +68182,7 @@
         <v>21.874011479980915</v>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A181" s="113">
         <v>4</v>
       </c>
@@ -68266,7 +68266,7 @@
         <v>-0.24809088830402004</v>
       </c>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A182" s="113">
         <v>4</v>
       </c>
@@ -68350,7 +68350,7 @@
         <v>0.67617777434136883</v>
       </c>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A183" s="113">
         <v>4</v>
       </c>
@@ -68434,7 +68434,7 @@
         <v>47.515364120089828</v>
       </c>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A184" s="113">
         <v>4</v>
       </c>
@@ -68518,7 +68518,7 @@
         <v>58.912795542325199</v>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A185" s="113">
         <v>4</v>
       </c>
@@ -68602,7 +68602,7 @@
         <v>1.3923112348113165</v>
       </c>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A186" s="113">
         <v>4</v>
       </c>
@@ -68686,7 +68686,7 @@
         <v>16.694710423090786</v>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A187" s="113">
         <v>4</v>
       </c>
@@ -68770,7 +68770,7 @@
         <v>24.078051020677282</v>
       </c>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A188" s="113">
         <v>4</v>
       </c>
@@ -68854,7 +68854,7 @@
         <v>0.40395757047839709</v>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A189" s="113">
         <v>4</v>
       </c>
@@ -68938,7 +68938,7 @@
         <v>92.329184705310922</v>
       </c>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A190" s="113">
         <v>4</v>
       </c>
@@ -69022,7 +69022,7 @@
         <v>48.6049270531419</v>
       </c>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A191" s="113">
         <v>4</v>
       </c>
@@ -69106,7 +69106,7 @@
         <v>27.430565183215183</v>
       </c>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A192" s="113">
         <v>4</v>
       </c>
@@ -69190,7 +69190,7 @@
         <v>29.263379919854952</v>
       </c>
     </row>
-    <row r="193" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A193" s="113">
         <v>4</v>
       </c>
@@ -69274,7 +69274,7 @@
         <v>46.25733072637361</v>
       </c>
     </row>
-    <row r="194" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A194" s="113">
         <v>4</v>
       </c>
@@ -69358,7 +69358,7 @@
         <v>29.047199241718502</v>
       </c>
     </row>
-    <row r="195" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A195" s="113">
         <v>4</v>
       </c>
@@ -69442,7 +69442,7 @@
         <v>34.313415944129403</v>
       </c>
     </row>
-    <row r="196" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A196" s="113">
         <v>4</v>
       </c>
@@ -69526,7 +69526,7 @@
         <v>22.489827848743982</v>
       </c>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A197" s="113">
         <v>4</v>
       </c>
@@ -69610,7 +69610,7 @@
         <v>5.4339440184603136</v>
       </c>
     </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A198" s="113">
         <v>4</v>
       </c>
@@ -69694,7 +69694,7 @@
         <v>14.238793509131487</v>
       </c>
     </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A199" s="113">
         <v>4</v>
       </c>
@@ -69778,7 +69778,7 @@
         <v>56.457663653641802</v>
       </c>
     </row>
-    <row r="200" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A200" s="113">
         <v>4</v>
       </c>
@@ -69862,7 +69862,7 @@
         <v>3.4408337352331841</v>
       </c>
     </row>
-    <row r="201" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A201" s="113">
         <v>4</v>
       </c>
@@ -69946,7 +69946,7 @@
         <v>38.363478358238723</v>
       </c>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A202" s="113">
         <v>4</v>
       </c>
@@ -70030,7 +70030,7 @@
         <v>20.927006780027124</v>
       </c>
     </row>
-    <row r="203" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A203" s="113">
         <v>4</v>
       </c>
@@ -70114,7 +70114,7 @@
         <v>14.675003840356471</v>
       </c>
     </row>
-    <row r="204" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A204" s="113">
         <v>4</v>
       </c>
@@ -70198,7 +70198,7 @@
         <v>28.207043493018169</v>
       </c>
     </row>
-    <row r="205" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A205" s="113">
         <v>5</v>
       </c>
@@ -70282,7 +70282,7 @@
         <v>2.2178689712948341</v>
       </c>
     </row>
-    <row r="206" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A206" s="113">
         <v>5</v>
       </c>
@@ -70366,7 +70366,7 @@
         <v>-29.067191257081681</v>
       </c>
     </row>
-    <row r="207" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A207" s="113">
         <v>5</v>
       </c>
@@ -70450,7 +70450,7 @@
         <v>-7.0850815603695771</v>
       </c>
     </row>
-    <row r="208" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A208" s="113"/>
       <c r="B208" s="113"/>
       <c r="C208" s="113"/>
@@ -70520,7 +70520,7 @@
         <v>15.226058928929922</v>
       </c>
     </row>
-    <row r="209" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A209" s="113"/>
       <c r="B209" s="113"/>
       <c r="C209" s="113"/>
@@ -70590,7 +70590,7 @@
         <v>20.848897176604098</v>
       </c>
     </row>
-    <row r="210" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A210" s="113">
         <v>5</v>
       </c>
@@ -70676,7 +70676,7 @@
         <v>4.0862288299692295</v>
       </c>
     </row>
-    <row r="211" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A211" s="113">
         <v>5</v>
       </c>
@@ -70760,7 +70760,7 @@
         <v>12.583570342679096</v>
       </c>
     </row>
-    <row r="212" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A212" s="113">
         <v>5</v>
       </c>
@@ -70844,7 +70844,7 @@
         <v>15.631225582812824</v>
       </c>
     </row>
-    <row r="213" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A213" s="113">
         <v>5</v>
       </c>
@@ -70928,7 +70928,7 @@
         <v>11.076435865631229</v>
       </c>
     </row>
-    <row r="214" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A214" s="113">
         <v>5</v>
       </c>
@@ -71012,7 +71012,7 @@
         <v>11.840581801909611</v>
       </c>
     </row>
-    <row r="215" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A215" s="113">
         <v>5</v>
       </c>
@@ -71096,7 +71096,7 @@
         <v>15.895099035101445</v>
       </c>
     </row>
-    <row r="216" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A216" s="113">
         <v>5</v>
       </c>
@@ -71180,7 +71180,7 @@
         <v>42.676780867776372</v>
       </c>
     </row>
-    <row r="217" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A217" s="113">
         <v>5</v>
       </c>
@@ -71264,7 +71264,7 @@
         <v>244.02071483255574</v>
       </c>
     </row>
-    <row r="218" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A218" s="113">
         <v>5</v>
       </c>
@@ -71348,7 +71348,7 @@
         <v>101.80842893481979</v>
       </c>
     </row>
-    <row r="219" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A219" s="113">
         <v>5</v>
       </c>
@@ -71432,7 +71432,7 @@
         <v>62.749917582221038</v>
       </c>
     </row>
-    <row r="220" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A220" s="113">
         <v>5</v>
       </c>
@@ -71516,7 +71516,7 @@
         <v>7.1292626649710478</v>
       </c>
     </row>
-    <row r="221" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A221" s="113">
         <v>5</v>
       </c>
@@ -71600,7 +71600,7 @@
         <v>72.068670081975043</v>
       </c>
     </row>
-    <row r="222" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A222" s="113"/>
       <c r="B222" s="113"/>
       <c r="C222" s="113"/>
@@ -71670,7 +71670,7 @@
         <v>28.856639794785362</v>
       </c>
     </row>
-    <row r="223" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A223" s="113">
         <v>5</v>
       </c>
@@ -71754,7 +71754,7 @@
         <v>103.11642156628275</v>
       </c>
     </row>
-    <row r="224" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A224" s="113">
         <v>5</v>
       </c>
@@ -71838,7 +71838,7 @@
         <v>91.941435918385665</v>
       </c>
     </row>
-    <row r="225" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A225" s="113">
         <v>5</v>
       </c>
@@ -71922,7 +71922,7 @@
         <v>31.029096101204967</v>
       </c>
     </row>
-    <row r="226" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A226" s="113">
         <v>5</v>
       </c>
@@ -72006,7 +72006,7 @@
         <v>15.034134433109525</v>
       </c>
     </row>
-    <row r="227" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A227" s="113">
         <v>5</v>
       </c>
@@ -72090,7 +72090,7 @@
         <v>16.193166923064162</v>
       </c>
     </row>
-    <row r="228" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A228" s="113">
         <v>5</v>
       </c>
@@ -72174,7 +72174,7 @@
         <v>66.198496726406205</v>
       </c>
     </row>
-    <row r="229" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A229" s="113">
         <v>5</v>
       </c>
@@ -72258,7 +72258,7 @@
         <v>18.950765780398893</v>
       </c>
     </row>
-    <row r="230" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A230" s="113">
         <v>5</v>
       </c>
@@ -72342,7 +72342,7 @@
         <v>53.753252547172892</v>
       </c>
     </row>
-    <row r="231" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A231" s="113">
         <v>5</v>
       </c>
@@ -72426,7 +72426,7 @@
         <v>17.95273108781803</v>
       </c>
     </row>
-    <row r="232" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A232" s="113">
         <v>5</v>
       </c>
@@ -72510,7 +72510,7 @@
         <v>1.634206319258702</v>
       </c>
     </row>
-    <row r="233" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A233" s="113">
         <v>5</v>
       </c>
@@ -72594,7 +72594,7 @@
         <v>20.688137399751394</v>
       </c>
     </row>
-    <row r="234" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A234" s="113">
         <v>5</v>
       </c>
@@ -72678,7 +72678,7 @@
         <v>30.384162778023253</v>
       </c>
     </row>
-    <row r="235" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A235" s="113"/>
       <c r="B235" s="113"/>
       <c r="C235" s="113"/>
@@ -72748,7 +72748,7 @@
         <v>28.252942792998947</v>
       </c>
     </row>
-    <row r="236" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A236" s="113">
         <v>5</v>
       </c>
@@ -72832,7 +72832,7 @@
         <v>-3.0089019234891268</v>
       </c>
     </row>
-    <row r="237" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A237" s="113">
         <v>5</v>
       </c>
@@ -72916,7 +72916,7 @@
         <v>57.815553360107685</v>
       </c>
     </row>
-    <row r="238" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A238" s="113">
         <v>5</v>
       </c>
@@ -73000,7 +73000,7 @@
         <v>65.687208062810143</v>
       </c>
     </row>
-    <row r="239" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A239" s="113">
         <v>5</v>
       </c>
@@ -73084,7 +73084,7 @@
         <v>-4.633283040023084</v>
       </c>
     </row>
-    <row r="240" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A240" s="113">
         <v>5</v>
       </c>
@@ -73168,7 +73168,7 @@
         <v>26.451690525446377</v>
       </c>
     </row>
-    <row r="241" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A241" s="113">
         <v>5</v>
       </c>
@@ -73252,7 +73252,7 @@
         <v>43.661908292766952</v>
       </c>
     </row>
-    <row r="242" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A242" s="113">
         <v>5</v>
       </c>
@@ -73336,7 +73336,7 @@
         <v>12.624351719259241</v>
       </c>
     </row>
-    <row r="243" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A243" s="113">
         <v>5</v>
       </c>
@@ -73420,7 +73420,7 @@
         <v>62.060389842455436</v>
       </c>
     </row>
-    <row r="244" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A244" s="113">
         <v>5</v>
       </c>
@@ -73504,7 +73504,7 @@
         <v>20.66597172935225</v>
       </c>
     </row>
-    <row r="245" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A245" s="113">
         <v>5</v>
       </c>
@@ -73588,7 +73588,7 @@
         <v>5.0315167530978755</v>
       </c>
     </row>
-    <row r="246" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A246" s="113">
         <v>5</v>
       </c>
@@ -73672,7 +73672,7 @@
         <v>25.484791558618713</v>
       </c>
     </row>
-    <row r="247" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A247" s="113">
         <v>5</v>
       </c>
@@ -73756,7 +73756,7 @@
         <v>20.134633735242602</v>
       </c>
     </row>
-    <row r="248" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A248" s="113"/>
       <c r="B248" s="113"/>
       <c r="C248" s="113"/>
@@ -73826,7 +73826,7 @@
         <v>28.368657052848523</v>
       </c>
     </row>
-    <row r="249" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A249" s="113">
         <v>5</v>
       </c>
@@ -73910,7 +73910,7 @@
         <v>-30.984842620815908</v>
       </c>
     </row>
-    <row r="250" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A250" s="113">
         <v>5</v>
       </c>
@@ -73994,7 +73994,7 @@
         <v>83.202717688830589</v>
       </c>
     </row>
-    <row r="251" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A251" s="113">
         <v>5</v>
       </c>
@@ -74078,7 +74078,7 @@
         <v>52.616769330842139</v>
       </c>
     </row>
-    <row r="252" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A252" s="113">
         <v>5</v>
       </c>
@@ -74162,7 +74162,7 @@
         <v>-39.452784338689369</v>
       </c>
     </row>
-    <row r="253" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A253" s="113">
         <v>5</v>
       </c>
@@ -74246,7 +74246,7 @@
         <v>12.846971974278532</v>
       </c>
     </row>
-    <row r="254" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A254" s="113">
         <v>6</v>
       </c>
@@ -74332,7 +74332,7 @@
         <v>-0.39268624835830929</v>
       </c>
     </row>
-    <row r="255" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A255" s="113">
         <v>6</v>
       </c>
@@ -74418,7 +74418,7 @@
         <v>-10.295699724232055</v>
       </c>
     </row>
-    <row r="256" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A256" s="113">
         <v>6</v>
       </c>
@@ -74502,7 +74502,7 @@
         <v>56.798316471582396</v>
       </c>
     </row>
-    <row r="257" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A257" s="113">
         <v>6</v>
       </c>
@@ -74586,7 +74586,7 @@
         <v>2.6481708224523888</v>
       </c>
     </row>
-    <row r="258" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A258" s="113">
         <v>6</v>
       </c>
@@ -74670,7 +74670,7 @@
         <v>14.114923360653009</v>
       </c>
     </row>
-    <row r="259" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A259" s="113">
         <v>6</v>
       </c>
@@ -74756,7 +74756,7 @@
         <v>3.8364444926330954</v>
       </c>
     </row>
-    <row r="260" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A260" s="113">
         <v>6</v>
       </c>
@@ -74840,7 +74840,7 @@
         <v>62.353849031397949</v>
       </c>
     </row>
-    <row r="261" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A261" s="113"/>
       <c r="B261" s="113"/>
       <c r="C261" s="113"/>
@@ -74910,7 +74910,7 @@
         <v>22.713428388188017</v>
       </c>
     </row>
-    <row r="262" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A262" s="113">
         <v>6</v>
       </c>
@@ -74996,7 +74996,7 @@
         <v>13.937121750733361</v>
       </c>
     </row>
-    <row r="263" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A263" s="113">
         <v>6</v>
       </c>
@@ -75080,7 +75080,7 @@
         <v>21.083863890092314</v>
       </c>
     </row>
-    <row r="264" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A264" s="113">
         <v>6</v>
       </c>
@@ -75164,7 +75164,7 @@
         <v>1.6040980210352274</v>
       </c>
     </row>
-    <row r="265" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A265" s="113">
         <v>6</v>
       </c>
@@ -75248,7 +75248,7 @@
         <v>116.83977952817725</v>
       </c>
     </row>
-    <row r="266" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A266" s="113">
         <v>6</v>
       </c>
@@ -75332,7 +75332,7 @@
         <v>44.798088951303328</v>
       </c>
     </row>
-    <row r="267" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A267" s="113">
         <v>6</v>
       </c>
@@ -75416,7 +75416,7 @@
         <v>41.700755168128097</v>
       </c>
     </row>
-    <row r="268" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A268" s="113">
         <v>6</v>
       </c>
@@ -75500,7 +75500,7 @@
         <v>23.471851059846394</v>
       </c>
     </row>
-    <row r="269" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A269" s="113">
         <v>6</v>
       </c>
@@ -75584,7 +75584,7 @@
         <v>14.595878615502045</v>
       </c>
     </row>
-    <row r="270" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A270" s="113">
         <v>6</v>
       </c>
@@ -75668,7 +75668,7 @@
         <v>20.454548480355328</v>
       </c>
     </row>
-    <row r="271" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A271" s="113">
         <v>6</v>
       </c>
@@ -75754,7 +75754,7 @@
         <v>141.48101923319612</v>
       </c>
     </row>
-    <row r="272" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A272" s="113">
         <v>6</v>
       </c>
@@ -75838,7 +75838,7 @@
         <v>34.766715760867761</v>
       </c>
     </row>
-    <row r="273" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A273" s="113">
         <v>6</v>
       </c>
@@ -75922,7 +75922,7 @@
         <v>57.482812693439023</v>
       </c>
     </row>
-    <row r="274" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A274" s="113"/>
       <c r="B274" s="113"/>
       <c r="C274" s="113"/>
@@ -75992,7 +75992,7 @@
         <v>23.990205682900001</v>
       </c>
     </row>
-    <row r="275" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A275" s="113">
         <v>6</v>
       </c>
@@ -76076,7 +76076,7 @@
         <v>85.887697417803551</v>
       </c>
     </row>
-    <row r="276" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A276" s="113">
         <v>6</v>
       </c>
@@ -76160,7 +76160,7 @@
         <v>0.36601482878539926</v>
       </c>
     </row>
-    <row r="277" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A277" s="113">
         <v>6</v>
       </c>
@@ -76246,7 +76246,7 @@
         <v>10.202736430073855</v>
       </c>
     </row>
-    <row r="278" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A278" s="113">
         <v>6</v>
       </c>
@@ -76330,7 +76330,7 @@
         <v>9.1401105730204435</v>
       </c>
     </row>
-    <row r="279" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A279" s="113">
         <v>6</v>
       </c>
@@ -76414,7 +76414,7 @@
         <v>-13.127704953059816</v>
       </c>
     </row>
-    <row r="280" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A280" s="113">
         <v>6</v>
       </c>
@@ -76498,7 +76498,7 @@
         <v>60.097887069845427</v>
       </c>
     </row>
-    <row r="281" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A281" s="113">
         <v>6</v>
       </c>
@@ -76582,7 +76582,7 @@
         <v>21.954929857894712</v>
       </c>
     </row>
-    <row r="282" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A282" s="113">
         <v>6</v>
       </c>
@@ -76666,7 +76666,7 @@
         <v>5.6233885447620757</v>
       </c>
     </row>
-    <row r="283" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A283" s="113">
         <v>6</v>
       </c>
@@ -76750,7 +76750,7 @@
         <v>19.072790039722509</v>
       </c>
     </row>
-    <row r="284" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A284" s="113">
         <v>6</v>
       </c>
@@ -76834,7 +76834,7 @@
         <v>9.6755920247382221</v>
       </c>
     </row>
-    <row r="285" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A285" s="113">
         <v>6</v>
       </c>
@@ -76918,7 +76918,7 @@
         <v>-7.9302553790139285</v>
       </c>
     </row>
-    <row r="286" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A286" s="113">
         <v>6</v>
       </c>
@@ -77002,7 +77002,7 @@
         <v>46.990823855592723</v>
       </c>
     </row>
-    <row r="287" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A287" s="113"/>
       <c r="B287" s="113"/>
       <c r="C287" s="113"/>
@@ -77072,7 +77072,7 @@
         <v>23.911406684400394</v>
       </c>
     </row>
-    <row r="288" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A288" s="113">
         <v>6</v>
       </c>
@@ -77156,7 +77156,7 @@
         <v>16.479241666313982</v>
       </c>
     </row>
-    <row r="289" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A289" s="113">
         <v>6</v>
       </c>
@@ -77240,7 +77240,7 @@
         <v>-2.7212487460914758</v>
       </c>
     </row>
-    <row r="290" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A290" s="113">
         <v>6</v>
       </c>
@@ -77324,7 +77324,7 @@
         <v>15.213271280793972</v>
       </c>
     </row>
-    <row r="291" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A291" s="113">
         <v>6</v>
       </c>
@@ -77408,7 +77408,7 @@
         <v>14.899978774958189</v>
       </c>
     </row>
-    <row r="292" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A292" s="113">
         <v>6</v>
       </c>
@@ -77492,7 +77492,7 @@
         <v>10.900371856668034</v>
       </c>
     </row>
-    <row r="293" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A293" s="113">
         <v>6</v>
       </c>
@@ -77576,7 +77576,7 @@
         <v>15.144731970386793</v>
       </c>
     </row>
-    <row r="294" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A294" s="113">
         <v>6</v>
       </c>
@@ -77660,7 +77660,7 @@
         <v>7.2233405401389552</v>
       </c>
     </row>
-    <row r="295" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A295" s="113">
         <v>6</v>
       </c>
@@ -77744,7 +77744,7 @@
         <v>-2.2736211230101055</v>
       </c>
     </row>
-    <row r="296" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A296" s="113">
         <v>6</v>
       </c>
@@ -77828,7 +77828,7 @@
         <v>22.976294425758326</v>
       </c>
     </row>
-    <row r="297" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A297" s="113">
         <v>6</v>
       </c>
@@ -77912,7 +77912,7 @@
         <v>17.191448139026733</v>
       </c>
     </row>
-    <row r="298" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A298" s="113">
         <v>6</v>
       </c>
@@ -77996,7 +77996,7 @@
         <v>-1.248599842509357</v>
       </c>
     </row>
-    <row r="299" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A299" s="113">
         <v>6</v>
       </c>
@@ -78080,7 +78080,7 @@
         <v>68.450233700250166</v>
       </c>
     </row>
-    <row r="300" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A300" s="113">
         <v>6</v>
       </c>
@@ -78164,7 +78164,7 @@
         <v>26.04657609005967</v>
       </c>
     </row>
-    <row r="301" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A301" s="113">
         <v>6</v>
       </c>
@@ -78248,7 +78248,7 @@
         <v>3.5940105932064093</v>
       </c>
     </row>
-    <row r="302" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A302" s="113">
         <v>6</v>
       </c>
@@ -78332,7 +78332,7 @@
         <v>13.537966303087678</v>
       </c>
     </row>
-    <row r="303" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:28" x14ac:dyDescent="0.35">
       <c r="F303" s="9"/>
     </row>
   </sheetData>
